--- a/outputs/hdlbits-archive/HDLBits_Tracker.xlsx
+++ b/outputs/hdlbits-archive/HDLBits_Tracker.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R381a78ab89bd4981"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="2" r:id="Rcabe1381b9a24723"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R7f178ae651344d17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="2" r:id="Raaacd0dad0a3427b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
     <x:numFmt numFmtId="201" formatCode="0"/>
     <x:numFmt numFmtId="202" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="16">
+  <x:fonts count="18">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -110,8 +110,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -146,6 +156,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF3F3F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF99"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF002060"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -263,7 +283,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="149">
+  <x:cellXfs count="175">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -599,6 +619,76 @@
     <x:xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -609,7 +699,7 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFCCFFCC"/>
         </x:patternFill>
       </x:fill>
@@ -620,7 +710,7 @@
         <x:color rgb="FF9C6500"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFFF99"/>
         </x:patternFill>
       </x:fill>
@@ -630,9 +720,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HDLBitsTracker" displayName="HDLBitsTracker" ref="A5:T120" headerRowCount="1">
-  <x:autoFilter ref="A5:T120"/>
-  <x:tableColumns count="20">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HDLBitsTracker" displayName="HDLBitsTracker" ref="A5:U120" headerRowCount="1">
+  <x:autoFilter ref="A5:U120"/>
+  <x:tableColumns count="21">
     <x:tableColumn id="1" name="Problem #"/>
     <x:tableColumn id="2" name="Category"/>
     <x:tableColumn id="3" name="Section"/>
@@ -652,7 +742,8 @@
     <x:tableColumn id="17" name="Screenshot"/>
     <x:tableColumn id="18" name="Verilog solution"/>
     <x:tableColumn id="19" name="HDLBits page"/>
-    <x:tableColumn id="20" name="What I learned"/>
+    <x:tableColumn id="20" name="What the problem asks"/>
+    <x:tableColumn id="21" name="What I learned"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </x:table>
@@ -1206,7 +1297,7 @@
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
       <x:c r="A20" s="65" t="str">
-        <x:v>Use the blue link columns to open the local note, screenshot, solution, or HDLBits page.</x:v>
+        <x:v>Use the blue link columns to open the GitHub note, full-size screenshot, saved solution, or HDLBits page.</x:v>
       </x:c>
       <x:c r="B20" s="65"/>
       <x:c r="C20" s="65"/>
@@ -1309,11 +1400,12 @@
     <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="30" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="30" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="30" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="34" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="38" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="17" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="17" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="14" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="48" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1364,7 +1456,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="43" t="str">
-        <x:v>Rows 1–114 are archived successful submissions. Row 115 is the current attempted problem. Yellow cells are for your revision notes.</x:v>
+        <x:v>Rows 1–114 are archived successful submissions. Row 115 is the current attempted problem. Use the blue public links to open each note, full-size screenshot, solution, or HDLBits page. Yellow cells are for your revision notes.</x:v>
       </x:c>
       <x:c r="B3" s="43"/>
       <x:c r="C3" s="43"/>
@@ -1454,23 +1546,26 @@
       <x:c r="O5" s="127" t="str">
         <x:v>Success rate</x:v>
       </x:c>
-      <x:c r="P5" s="127" t="str">
+      <x:c r="P5" s="169" t="str">
         <x:v>Problem note</x:v>
       </x:c>
-      <x:c r="Q5" s="127" t="str">
+      <x:c r="Q5" s="169" t="str">
         <x:v>Screenshot</x:v>
       </x:c>
-      <x:c r="R5" s="127" t="str">
+      <x:c r="R5" s="169" t="str">
         <x:v>Verilog solution</x:v>
       </x:c>
-      <x:c r="S5" s="127" t="str">
+      <x:c r="S5" s="169" t="str">
         <x:v>HDLBits page</x:v>
       </x:c>
-      <x:c r="T5" s="127" t="str">
+      <x:c r="T5" s="169" t="str">
+        <x:v>What the problem asks</x:v>
+      </x:c>
+      <x:c r="U5" s="174" t="str">
         <x:v>What I learned</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="34" customHeight="1">
+    <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="128" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -1514,21 +1609,28 @@
       <x:c r="O6" s="132" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P6" s="133" t="str">
-        <x:v>../../problems/Day 01/001-wire.md</x:v>
-      </x:c>
-      <x:c r="Q6" s="133" t="str">
-        <x:v>../../images/Day 01/001-wire.png</x:v>
-      </x:c>
-      <x:c r="R6" s="133" t="str">
-        <x:v>../../solutions/Day 01/001-wire.sv</x:v>
-      </x:c>
-      <x:c r="S6" s="133" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/wire</x:v>
-      </x:c>
-      <x:c r="T6" s="134" t="str"/>
-    </x:row>
-    <x:row r="7" ht="34" customHeight="1">
+      <x:c r="P6" s="152" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/001-wire.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/001-wire.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q6" s="152" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/001-wire.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/001-wire.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R6" s="152" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/001-wire.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/001-wire.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S6" s="152" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/wire","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/wire, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T6" s="161" t="str">
+        <x:v>Connect the single input directly to the output so the module behaves exactly like a wire.</x:v>
+      </x:c>
+      <x:c r="U6" s="168"/>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
       <x:c r="A7" s="135" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -1572,21 +1674,28 @@
       <x:c r="O7" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P7" s="140" t="str">
-        <x:v>../../problems/Day 01/002-wire4.md</x:v>
-      </x:c>
-      <x:c r="Q7" s="140" t="str">
-        <x:v>../../images/Day 01/002-wire4.png</x:v>
-      </x:c>
-      <x:c r="R7" s="140" t="str">
-        <x:v>../../solutions/Day 01/002-wire4.sv</x:v>
-      </x:c>
-      <x:c r="S7" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/wire4</x:v>
-      </x:c>
-      <x:c r="T7" s="141" t="str"/>
-    </x:row>
-    <x:row r="8" ht="34" customHeight="1">
+      <x:c r="P7" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/002-wire4.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/002-wire4.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q7" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/002-wire4.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/002-wire4.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R7" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/002-wire4.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/002-wire4.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S7" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/wire4","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/wire4, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T7" s="162" t="str">
+        <x:v>Create the requested one-to-one and fan-out wire connections between the named inputs and outputs.</x:v>
+      </x:c>
+      <x:c r="U7" s="168"/>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="135" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -1630,21 +1739,28 @@
       <x:c r="O8" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P8" s="140" t="str">
-        <x:v>../../problems/Day 01/003-notgate.md</x:v>
-      </x:c>
-      <x:c r="Q8" s="140" t="str">
-        <x:v>../../images/Day 01/003-notgate.png</x:v>
-      </x:c>
-      <x:c r="R8" s="140" t="str">
-        <x:v>../../solutions/Day 01/003-notgate.sv</x:v>
-      </x:c>
-      <x:c r="S8" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/notgate</x:v>
-      </x:c>
-      <x:c r="T8" s="141" t="str"/>
-    </x:row>
-    <x:row r="9" ht="34" customHeight="1">
+      <x:c r="P8" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/003-notgate.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/003-notgate.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q8" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/003-notgate.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/003-notgate.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R8" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/003-notgate.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/003-notgate.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S8" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/notgate","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/notgate, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T8" s="162" t="str">
+        <x:v>Drive the output with the logical inverse of the input, implementing a NOT gate.</x:v>
+      </x:c>
+      <x:c r="U8" s="168"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="135" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -1688,21 +1804,28 @@
       <x:c r="O9" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P9" s="140" t="str">
-        <x:v>../../problems/Day 02/004-andgate.md</x:v>
-      </x:c>
-      <x:c r="Q9" s="140" t="str">
-        <x:v>../../images/Day 02/004-andgate.png</x:v>
-      </x:c>
-      <x:c r="R9" s="140" t="str">
-        <x:v>../../solutions/Day 02/004-andgate.sv</x:v>
-      </x:c>
-      <x:c r="S9" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/andgate</x:v>
-      </x:c>
-      <x:c r="T9" s="141" t="str"/>
-    </x:row>
-    <x:row r="10" ht="34" customHeight="1">
+      <x:c r="P9" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/004-andgate.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/004-andgate.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q9" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/004-andgate.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/004-andgate.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R9" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/004-andgate.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/004-andgate.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S9" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/andgate","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/andgate, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T9" s="162" t="str">
+        <x:v>Produce an output that is high only when both input signals are high.</x:v>
+      </x:c>
+      <x:c r="U9" s="168"/>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="135" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -1746,21 +1869,28 @@
       <x:c r="O10" s="139" t="n">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P10" s="140" t="str">
-        <x:v>../../problems/Day 02/005-norgate.md</x:v>
-      </x:c>
-      <x:c r="Q10" s="140" t="str">
-        <x:v>../../images/Day 02/005-norgate.png</x:v>
-      </x:c>
-      <x:c r="R10" s="140" t="str">
-        <x:v>../../solutions/Day 02/005-norgate.sv</x:v>
-      </x:c>
-      <x:c r="S10" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/norgate</x:v>
-      </x:c>
-      <x:c r="T10" s="141" t="str"/>
-    </x:row>
-    <x:row r="11" ht="34" customHeight="1">
+      <x:c r="P10" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/005-norgate.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/005-norgate.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q10" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/005-norgate.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/005-norgate.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R10" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/005-norgate.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/005-norgate.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S10" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/norgate","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/norgate, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T10" s="162" t="str">
+        <x:v>Implement a NOR gate: OR the inputs and invert the result.</x:v>
+      </x:c>
+      <x:c r="U10" s="168"/>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="135" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -1804,21 +1934,28 @@
       <x:c r="O11" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P11" s="140" t="str">
-        <x:v>../../problems/Day 02/006-xnorgate.md</x:v>
-      </x:c>
-      <x:c r="Q11" s="140" t="str">
-        <x:v>../../images/Day 02/006-xnorgate.png</x:v>
-      </x:c>
-      <x:c r="R11" s="140" t="str">
-        <x:v>../../solutions/Day 02/006-xnorgate.sv</x:v>
-      </x:c>
-      <x:c r="S11" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/xnorgate</x:v>
-      </x:c>
-      <x:c r="T11" s="141" t="str"/>
-    </x:row>
-    <x:row r="12" ht="34" customHeight="1">
+      <x:c r="P11" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/006-xnorgate.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/006-xnorgate.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q11" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/006-xnorgate.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/006-xnorgate.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R11" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/006-xnorgate.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/006-xnorgate.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S11" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/xnorgate","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/xnorgate, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T11" s="162" t="str">
+        <x:v>Implement an XNOR gate whose output is high when the two inputs have equal values.</x:v>
+      </x:c>
+      <x:c r="U11" s="168"/>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="135" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -1862,21 +1999,28 @@
       <x:c r="O12" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P12" s="140" t="str">
-        <x:v>../../problems/Day 02/007-wire_decl.md</x:v>
-      </x:c>
-      <x:c r="Q12" s="140" t="str">
-        <x:v>../../images/Day 02/007-wire_decl.png</x:v>
-      </x:c>
-      <x:c r="R12" s="140" t="str">
-        <x:v>../../solutions/Day 02/007-wire_decl.sv</x:v>
-      </x:c>
-      <x:c r="S12" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/wire_decl</x:v>
-      </x:c>
-      <x:c r="T12" s="141" t="str"/>
-    </x:row>
-    <x:row r="13" ht="34" customHeight="1">
+      <x:c r="P12" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/007-wire_decl.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/007-wire_decl.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q12" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/007-wire_decl.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/007-wire_decl.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R12" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/007-wire_decl.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/007-wire_decl.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S12" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/wire_decl","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/wire_decl, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T12" s="162" t="str">
+        <x:v>Declare intermediate wires and connect the supplied gates so the module matches the shown circuit diagram.</x:v>
+      </x:c>
+      <x:c r="U12" s="168"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
       <x:c r="A13" s="135" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -1920,21 +2064,28 @@
       <x:c r="O13" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P13" s="140" t="str">
-        <x:v>../../problems/Day 01/008-7458.md</x:v>
-      </x:c>
-      <x:c r="Q13" s="140" t="str">
-        <x:v>../../images/Day 01/008-7458.png</x:v>
-      </x:c>
-      <x:c r="R13" s="140" t="str">
-        <x:v>../../solutions/Day 01/008-7458.sv</x:v>
-      </x:c>
-      <x:c r="S13" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/7458</x:v>
-      </x:c>
-      <x:c r="T13" s="141" t="str"/>
-    </x:row>
-    <x:row r="14" ht="34" customHeight="1">
+      <x:c r="P13" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/008-7458.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/008-7458.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q13" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/008-7458.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/008-7458.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R13" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/008-7458.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/008-7458.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S13" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/7458","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/7458, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T13" s="162" t="str">
+        <x:v>Recreate the 7458-style sum-of-products circuit by combining several AND terms into two OR outputs.</x:v>
+      </x:c>
+      <x:c r="U13" s="168"/>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="135" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -1978,21 +2129,28 @@
       <x:c r="O14" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P14" s="140" t="str">
-        <x:v>../../problems/Day 01/009-vector0.md</x:v>
-      </x:c>
-      <x:c r="Q14" s="140" t="str">
-        <x:v>../../images/Day 01/009-vector0.png</x:v>
-      </x:c>
-      <x:c r="R14" s="140" t="str">
-        <x:v>../../solutions/Day 01/009-vector0.sv</x:v>
-      </x:c>
-      <x:c r="S14" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/vector0</x:v>
-      </x:c>
-      <x:c r="T14" s="141" t="str"/>
-    </x:row>
-    <x:row r="15" ht="34" customHeight="1">
+      <x:c r="P14" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/009-vector0.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/009-vector0.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q14" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/009-vector0.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/009-vector0.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R14" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/009-vector0.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/009-vector0.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S14" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vector0","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector0, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T14" s="162" t="str">
+        <x:v>Declare vector ports with the required widths and connect the complete input bus to the output bus.</x:v>
+      </x:c>
+      <x:c r="U14" s="168"/>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
       <x:c r="A15" s="135" t="n">
         <x:v>10</x:v>
       </x:c>
@@ -2036,21 +2194,28 @@
       <x:c r="O15" s="139" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="P15" s="140" t="str">
-        <x:v>../../problems/Day 01/010-vector1.md</x:v>
-      </x:c>
-      <x:c r="Q15" s="140" t="str">
-        <x:v>../../images/Day 01/010-vector1.png</x:v>
-      </x:c>
-      <x:c r="R15" s="140" t="str">
-        <x:v>../../solutions/Day 01/010-vector1.sv</x:v>
-      </x:c>
-      <x:c r="S15" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/vector1</x:v>
-      </x:c>
-      <x:c r="T15" s="141" t="str"/>
-    </x:row>
-    <x:row r="16" ht="34" customHeight="1">
+      <x:c r="P15" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/010-vector1.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/010-vector1.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q15" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/010-vector1.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/010-vector1.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R15" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/010-vector1.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/010-vector1.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S15" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vector1","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector1, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T15" s="162" t="str">
+        <x:v>Practice vector declarations, bit ordering, and selecting individual bits from buses with different index directions.</x:v>
+      </x:c>
+      <x:c r="U15" s="168"/>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="135" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -2094,21 +2259,28 @@
       <x:c r="O16" s="139" t="n">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P16" s="140" t="str">
-        <x:v>../../problems/Day 01/011-vector2.md</x:v>
-      </x:c>
-      <x:c r="Q16" s="140" t="str">
-        <x:v>../../images/Day 01/011-vector2.png</x:v>
-      </x:c>
-      <x:c r="R16" s="140" t="str">
-        <x:v>../../solutions/Day 01/011-vector2.sv</x:v>
-      </x:c>
-      <x:c r="S16" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/vector2</x:v>
-      </x:c>
-      <x:c r="T16" s="141" t="str"/>
-    </x:row>
-    <x:row r="17" ht="34" customHeight="1">
+      <x:c r="P16" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/011-vector2.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/011-vector2.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q16" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/011-vector2.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/011-vector2.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R16" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/011-vector2.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/011-vector2.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S16" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vector2","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector2, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T16" s="162" t="str">
+        <x:v>Split a 16-bit input vector into its upper and lower 8-bit halves and route them to separate outputs.</x:v>
+      </x:c>
+      <x:c r="U16" s="168"/>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="135" t="n">
         <x:v>12</x:v>
       </x:c>
@@ -2152,21 +2324,28 @@
       <x:c r="O17" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P17" s="140" t="str">
-        <x:v>../../problems/Day 01/012-vectorgates.md</x:v>
-      </x:c>
-      <x:c r="Q17" s="140" t="str">
-        <x:v>../../images/Day 01/012-vectorgates.png</x:v>
-      </x:c>
-      <x:c r="R17" s="140" t="str">
-        <x:v>../../solutions/Day 01/012-vectorgates.sv</x:v>
-      </x:c>
-      <x:c r="S17" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/vectorgates</x:v>
-      </x:c>
-      <x:c r="T17" s="141" t="str"/>
-    </x:row>
-    <x:row r="18" ht="34" customHeight="1">
+      <x:c r="P17" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/012-vectorgates.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/012-vectorgates.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q17" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/012-vectorgates.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/012-vectorgates.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R17" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/012-vectorgates.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/012-vectorgates.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S17" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vectorgates","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vectorgates, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T17" s="162" t="str">
+        <x:v>Apply bitwise OR, logical OR, and bitwise inversion to vectors so their different behaviours are visible.</x:v>
+      </x:c>
+      <x:c r="U17" s="168"/>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="135" t="n">
         <x:v>13</x:v>
       </x:c>
@@ -2210,21 +2389,28 @@
       <x:c r="O18" s="139" t="n">
         <x:v>0.13</x:v>
       </x:c>
-      <x:c r="P18" s="140" t="str">
-        <x:v>../../problems/Day 01/013-gates4.md</x:v>
-      </x:c>
-      <x:c r="Q18" s="140" t="str">
-        <x:v>../../images/Day 01/013-gates4.png</x:v>
-      </x:c>
-      <x:c r="R18" s="140" t="str">
-        <x:v>../../solutions/Day 01/013-gates4.sv</x:v>
-      </x:c>
-      <x:c r="S18" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/gates4</x:v>
-      </x:c>
-      <x:c r="T18" s="141" t="str"/>
-    </x:row>
-    <x:row r="19" ht="34" customHeight="1">
+      <x:c r="P18" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/013-gates4.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/013-gates4.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q18" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/013-gates4.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/013-gates4.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R18" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/013-gates4.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/013-gates4.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S18" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/gates4","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gates4, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T18" s="162" t="str">
+        <x:v>Use reduction operators to compute one-bit AND, OR, and XOR results across all four input bits.</x:v>
+      </x:c>
+      <x:c r="U18" s="168"/>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
       <x:c r="A19" s="135" t="n">
         <x:v>14</x:v>
       </x:c>
@@ -2268,21 +2454,28 @@
       <x:c r="O19" s="139" t="n">
         <x:v>0.13</x:v>
       </x:c>
-      <x:c r="P19" s="140" t="str">
-        <x:v>../../problems/Day 01/014-vector3.md</x:v>
-      </x:c>
-      <x:c r="Q19" s="140" t="str">
-        <x:v>../../images/Day 01/014-vector3.png</x:v>
-      </x:c>
-      <x:c r="R19" s="140" t="str">
-        <x:v>../../solutions/Day 01/014-vector3.sv</x:v>
-      </x:c>
-      <x:c r="S19" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/vector3</x:v>
-      </x:c>
-      <x:c r="T19" s="141" t="str"/>
-    </x:row>
-    <x:row r="20" ht="34" customHeight="1">
+      <x:c r="P19" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/014-vector3.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/014-vector3.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q19" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/014-vector3.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/014-vector3.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R19" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/014-vector3.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/014-vector3.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S19" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vector3","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector3, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T19" s="162" t="str">
+        <x:v>Use concatenation to regroup the input vectors and assign the requested output vectors in the specified bit order.</x:v>
+      </x:c>
+      <x:c r="U19" s="168"/>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="135" t="n">
         <x:v>15</x:v>
       </x:c>
@@ -2326,21 +2519,28 @@
       <x:c r="O20" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P20" s="140" t="str">
-        <x:v>../../problems/Day 01/015-vectorr.md</x:v>
-      </x:c>
-      <x:c r="Q20" s="140" t="str">
-        <x:v>../../images/Day 01/015-vectorr.png</x:v>
-      </x:c>
-      <x:c r="R20" s="140" t="str">
-        <x:v>../../solutions/Day 01/015-vectorr.sv</x:v>
-      </x:c>
-      <x:c r="S20" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/vectorr</x:v>
-      </x:c>
-      <x:c r="T20" s="141" t="str"/>
-    </x:row>
-    <x:row r="21" ht="34" customHeight="1">
+      <x:c r="P20" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/015-vectorr.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/015-vectorr.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q20" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/015-vectorr.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/015-vectorr.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R20" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/015-vectorr.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/015-vectorr.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S20" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vectorr","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vectorr, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T20" s="162" t="str">
+        <x:v>Reverse the bit order of the input vector so the most-significant and least-significant positions swap.</x:v>
+      </x:c>
+      <x:c r="U20" s="168"/>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
       <x:c r="A21" s="135" t="n">
         <x:v>16</x:v>
       </x:c>
@@ -2384,21 +2584,28 @@
       <x:c r="O21" s="139" t="n">
         <x:v>0.11</x:v>
       </x:c>
-      <x:c r="P21" s="140" t="str">
-        <x:v>../../problems/Day 01/016-vector4.md</x:v>
-      </x:c>
-      <x:c r="Q21" s="140" t="str">
-        <x:v>../../images/Day 01/016-vector4.png</x:v>
-      </x:c>
-      <x:c r="R21" s="140" t="str">
-        <x:v>../../solutions/Day 01/016-vector4.sv</x:v>
-      </x:c>
-      <x:c r="S21" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/vector4</x:v>
-      </x:c>
-      <x:c r="T21" s="141" t="str"/>
-    </x:row>
-    <x:row r="22" ht="34" customHeight="1">
+      <x:c r="P21" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/016-vector4.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2001/016-vector4.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q21" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/016-vector4.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2001/016-vector4.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R21" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/016-vector4.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2001/016-vector4.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S21" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vector4","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector4, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T21" s="162" t="str">
+        <x:v>Use the replication operator to repeat a bit pattern and form the required wider output vector.</x:v>
+      </x:c>
+      <x:c r="U21" s="168"/>
+    </x:row>
+    <x:row r="22" ht="42" customHeight="1">
       <x:c r="A22" s="135" t="n">
         <x:v>17</x:v>
       </x:c>
@@ -2442,21 +2649,28 @@
       <x:c r="O22" s="139" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P22" s="140" t="str">
-        <x:v>../../problems/Day 02/017-vector5.md</x:v>
-      </x:c>
-      <x:c r="Q22" s="140" t="str">
-        <x:v>../../images/Day 02/017-vector5.png</x:v>
-      </x:c>
-      <x:c r="R22" s="140" t="str">
-        <x:v>../../solutions/Day 02/017-vector5.sv</x:v>
-      </x:c>
-      <x:c r="S22" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/vector5</x:v>
-      </x:c>
-      <x:c r="T22" s="141" t="str"/>
-    </x:row>
-    <x:row r="23" ht="34" customHeight="1">
+      <x:c r="P22" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/017-vector5.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/017-vector5.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q22" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/017-vector5.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/017-vector5.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R22" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/017-vector5.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/017-vector5.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S22" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vector5","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector5, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T22" s="162" t="str">
+        <x:v>Combine replication and concatenation to build widened vectors and compare them bit by bit.</x:v>
+      </x:c>
+      <x:c r="U22" s="168"/>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
       <x:c r="A23" s="135" t="n">
         <x:v>18</x:v>
       </x:c>
@@ -2500,21 +2714,28 @@
       <x:c r="O23" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P23" s="140" t="str">
-        <x:v>../../problems/Day 02/018-module.md</x:v>
-      </x:c>
-      <x:c r="Q23" s="140" t="str">
-        <x:v>../../images/Day 02/018-module.png</x:v>
-      </x:c>
-      <x:c r="R23" s="140" t="str">
-        <x:v>../../solutions/Day 02/018-module.sv</x:v>
-      </x:c>
-      <x:c r="S23" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/module</x:v>
-      </x:c>
-      <x:c r="T23" s="141" t="str"/>
-    </x:row>
-    <x:row r="24" ht="34" customHeight="1">
+      <x:c r="P23" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/018-module.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/018-module.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q23" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/018-module.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/018-module.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R23" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/018-module.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/018-module.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S23" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T23" s="162" t="str">
+        <x:v>Instantiate the provided submodule and connect its input and output ports to the top-level module.</x:v>
+      </x:c>
+      <x:c r="U23" s="168"/>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
       <x:c r="A24" s="135" t="n">
         <x:v>19</x:v>
       </x:c>
@@ -2558,21 +2779,28 @@
       <x:c r="O24" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P24" s="140" t="str">
-        <x:v>../../problems/Day 02/019-module_pos.md</x:v>
-      </x:c>
-      <x:c r="Q24" s="140" t="str">
-        <x:v>../../images/Day 02/019-module_pos.png</x:v>
-      </x:c>
-      <x:c r="R24" s="140" t="str">
-        <x:v>../../solutions/Day 02/019-module_pos.sv</x:v>
-      </x:c>
-      <x:c r="S24" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/module_pos</x:v>
-      </x:c>
-      <x:c r="T24" s="141" t="str"/>
-    </x:row>
-    <x:row r="25" ht="34" customHeight="1">
+      <x:c r="P24" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/019-module_pos.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/019-module_pos.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q24" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/019-module_pos.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/019-module_pos.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R24" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/019-module_pos.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/019-module_pos.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S24" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_pos","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_pos, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T24" s="162" t="str">
+        <x:v>Instantiate a module and connect its ports by position, keeping the connection order exactly correct.</x:v>
+      </x:c>
+      <x:c r="U24" s="168"/>
+    </x:row>
+    <x:row r="25" ht="42" customHeight="1">
       <x:c r="A25" s="135" t="n">
         <x:v>20</x:v>
       </x:c>
@@ -2616,21 +2844,28 @@
       <x:c r="O25" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P25" s="140" t="str">
-        <x:v>../../problems/Day 02/020-module_name.md</x:v>
-      </x:c>
-      <x:c r="Q25" s="140" t="str">
-        <x:v>../../images/Day 02/020-module_name.png</x:v>
-      </x:c>
-      <x:c r="R25" s="140" t="str">
-        <x:v>../../solutions/Day 02/020-module_name.sv</x:v>
-      </x:c>
-      <x:c r="S25" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/module_name</x:v>
-      </x:c>
-      <x:c r="T25" s="141" t="str"/>
-    </x:row>
-    <x:row r="26" ht="34" customHeight="1">
+      <x:c r="P25" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/020-module_name.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/020-module_name.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q25" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/020-module_name.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/020-module_name.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R25" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/020-module_name.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/020-module_name.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S25" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_name","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_name, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T25" s="162" t="str">
+        <x:v>Instantiate a module and connect its ports by name so each signal is matched explicitly.</x:v>
+      </x:c>
+      <x:c r="U25" s="168"/>
+    </x:row>
+    <x:row r="26" ht="42" customHeight="1">
       <x:c r="A26" s="135" t="n">
         <x:v>21</x:v>
       </x:c>
@@ -2674,21 +2909,28 @@
       <x:c r="O26" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P26" s="140" t="str">
-        <x:v>../../problems/Day 02/021-module_shift.md</x:v>
-      </x:c>
-      <x:c r="Q26" s="140" t="str">
-        <x:v>../../images/Day 02/021-module_shift.png</x:v>
-      </x:c>
-      <x:c r="R26" s="140" t="str">
-        <x:v>../../solutions/Day 02/021-module_shift.sv</x:v>
-      </x:c>
-      <x:c r="S26" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/module_shift</x:v>
-      </x:c>
-      <x:c r="T26" s="141" t="str"/>
-    </x:row>
-    <x:row r="27" ht="34" customHeight="1">
+      <x:c r="P26" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/021-module_shift.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/021-module_shift.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q26" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/021-module_shift.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/021-module_shift.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R26" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/021-module_shift.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/021-module_shift.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S26" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_shift","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_shift, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T26" s="162" t="str">
+        <x:v>Chain three copies of the provided module so each stage feeds the next stage.</x:v>
+      </x:c>
+      <x:c r="U26" s="168"/>
+    </x:row>
+    <x:row r="27" ht="42" customHeight="1">
       <x:c r="A27" s="135" t="n">
         <x:v>22</x:v>
       </x:c>
@@ -2732,21 +2974,28 @@
       <x:c r="O27" s="139" t="n">
         <x:v>0.14</x:v>
       </x:c>
-      <x:c r="P27" s="140" t="str">
-        <x:v>../../problems/Day 02/022-module_shift8.md</x:v>
-      </x:c>
-      <x:c r="Q27" s="140" t="str">
-        <x:v>../../images/Day 02/022-module_shift8.png</x:v>
-      </x:c>
-      <x:c r="R27" s="140" t="str">
-        <x:v>../../solutions/Day 02/022-module_shift8.sv</x:v>
-      </x:c>
-      <x:c r="S27" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/module_shift8</x:v>
-      </x:c>
-      <x:c r="T27" s="141" t="str"/>
-    </x:row>
-    <x:row r="28" ht="34" customHeight="1">
+      <x:c r="P27" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/022-module_shift8.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/022-module_shift8.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q27" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/022-module_shift8.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/022-module_shift8.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R27" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/022-module_shift8.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/022-module_shift8.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S27" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_shift8","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_shift8, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T27" s="162" t="str">
+        <x:v>Instantiate the supplied 8-bit module and connect vector signals correctly through the hierarchy.</x:v>
+      </x:c>
+      <x:c r="U27" s="168"/>
+    </x:row>
+    <x:row r="28" ht="42" customHeight="1">
       <x:c r="A28" s="135" t="n">
         <x:v>23</x:v>
       </x:c>
@@ -2790,21 +3039,28 @@
       <x:c r="O28" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P28" s="140" t="str">
-        <x:v>../../problems/Day 02/023-module_add.md</x:v>
-      </x:c>
-      <x:c r="Q28" s="140" t="str">
-        <x:v>../../images/Day 02/023-module_add.png</x:v>
-      </x:c>
-      <x:c r="R28" s="140" t="str">
-        <x:v>../../solutions/Day 02/023-module_add.sv</x:v>
-      </x:c>
-      <x:c r="S28" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/module_add</x:v>
-      </x:c>
-      <x:c r="T28" s="141" t="str"/>
-    </x:row>
-    <x:row r="29" ht="34" customHeight="1">
+      <x:c r="P28" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/023-module_add.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/023-module_add.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q28" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/023-module_add.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/023-module_add.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R28" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/023-module_add.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/023-module_add.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S28" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_add","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_add, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T28" s="162" t="str">
+        <x:v>Instantiate two 16-bit adders to create a 32-bit adder, propagating the carry between the lower and upper halves.</x:v>
+      </x:c>
+      <x:c r="U28" s="168"/>
+    </x:row>
+    <x:row r="29" ht="42" customHeight="1">
       <x:c r="A29" s="135" t="n">
         <x:v>24</x:v>
       </x:c>
@@ -2848,21 +3104,28 @@
       <x:c r="O29" s="139" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P29" s="140" t="str">
-        <x:v>../../problems/Day 02/024-module_fadd.md</x:v>
-      </x:c>
-      <x:c r="Q29" s="140" t="str">
-        <x:v>../../images/Day 02/024-module_fadd.png</x:v>
-      </x:c>
-      <x:c r="R29" s="140" t="str">
-        <x:v>../../solutions/Day 02/024-module_fadd.sv</x:v>
-      </x:c>
-      <x:c r="S29" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/module_fadd</x:v>
-      </x:c>
-      <x:c r="T29" s="141" t="str"/>
-    </x:row>
-    <x:row r="30" ht="34" customHeight="1">
+      <x:c r="P29" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/024-module_fadd.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/024-module_fadd.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q29" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/024-module_fadd.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/024-module_fadd.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R29" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/024-module_fadd.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/024-module_fadd.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S29" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_fadd","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_fadd, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T29" s="162" t="str">
+        <x:v>Build a ripple-carry adder from full-adder instances and expose the carry produced by every bit position.</x:v>
+      </x:c>
+      <x:c r="U29" s="168"/>
+    </x:row>
+    <x:row r="30" ht="42" customHeight="1">
       <x:c r="A30" s="135" t="n">
         <x:v>25</x:v>
       </x:c>
@@ -2906,21 +3169,28 @@
       <x:c r="O30" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P30" s="140" t="str">
-        <x:v>../../problems/Day 02/025-module_cseladd.md</x:v>
-      </x:c>
-      <x:c r="Q30" s="140" t="str">
-        <x:v>../../images/Day 02/025-module_cseladd.png</x:v>
-      </x:c>
-      <x:c r="R30" s="140" t="str">
-        <x:v>../../solutions/Day 02/025-module_cseladd.sv</x:v>
-      </x:c>
-      <x:c r="S30" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/module_cseladd</x:v>
-      </x:c>
-      <x:c r="T30" s="141" t="str"/>
-    </x:row>
-    <x:row r="31" ht="34" customHeight="1">
+      <x:c r="P30" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/025-module_cseladd.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/025-module_cseladd.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q30" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/025-module_cseladd.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/025-module_cseladd.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R30" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/025-module_cseladd.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/025-module_cseladd.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S30" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_cseladd","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_cseladd, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T30" s="162" t="str">
+        <x:v>Build a carry-select adder by computing both possible upper sums and selecting the correct one using the lower carry.</x:v>
+      </x:c>
+      <x:c r="U30" s="168"/>
+    </x:row>
+    <x:row r="31" ht="42" customHeight="1">
       <x:c r="A31" s="135" t="n">
         <x:v>26</x:v>
       </x:c>
@@ -2964,21 +3234,28 @@
       <x:c r="O31" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P31" s="140" t="str">
-        <x:v>../../problems/Day 02/026-module_addsub.md</x:v>
-      </x:c>
-      <x:c r="Q31" s="140" t="str">
-        <x:v>../../images/Day 02/026-module_addsub.png</x:v>
-      </x:c>
-      <x:c r="R31" s="140" t="str">
-        <x:v>../../solutions/Day 02/026-module_addsub.sv</x:v>
-      </x:c>
-      <x:c r="S31" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/module_addsub</x:v>
-      </x:c>
-      <x:c r="T31" s="141" t="str"/>
-    </x:row>
-    <x:row r="32" ht="34" customHeight="1">
+      <x:c r="P31" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/026-module_addsub.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/026-module_addsub.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q31" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/026-module_addsub.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/026-module_addsub.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R31" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/026-module_addsub.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/026-module_addsub.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S31" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_addsub","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_addsub, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T31" s="162" t="str">
+        <x:v>Create an adder-subtractor by conditionally inverting one operand and using the mode signal as the initial carry-in.</x:v>
+      </x:c>
+      <x:c r="U31" s="168"/>
+    </x:row>
+    <x:row r="32" ht="42" customHeight="1">
       <x:c r="A32" s="135" t="n">
         <x:v>27</x:v>
       </x:c>
@@ -3022,21 +3299,28 @@
       <x:c r="O32" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P32" s="140" t="str">
-        <x:v>../../problems/Day 02/027-alwaysblock1.md</x:v>
-      </x:c>
-      <x:c r="Q32" s="140" t="str">
-        <x:v>../../images/Day 02/027-alwaysblock1.png</x:v>
-      </x:c>
-      <x:c r="R32" s="140" t="str">
-        <x:v>../../solutions/Day 02/027-alwaysblock1.sv</x:v>
-      </x:c>
-      <x:c r="S32" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/alwaysblock1</x:v>
-      </x:c>
-      <x:c r="T32" s="141" t="str"/>
-    </x:row>
-    <x:row r="33" ht="34" customHeight="1">
+      <x:c r="P32" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/027-alwaysblock1.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/027-alwaysblock1.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q32" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/027-alwaysblock1.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/027-alwaysblock1.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R32" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/027-alwaysblock1.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/027-alwaysblock1.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S32" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/alwaysblock1","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/alwaysblock1, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T32" s="162" t="str">
+        <x:v>Describe the same combinational logic with both a continuous assignment and an always block.</x:v>
+      </x:c>
+      <x:c r="U32" s="168"/>
+    </x:row>
+    <x:row r="33" ht="42" customHeight="1">
       <x:c r="A33" s="135" t="n">
         <x:v>28</x:v>
       </x:c>
@@ -3080,21 +3364,28 @@
       <x:c r="O33" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P33" s="140" t="str">
-        <x:v>../../problems/Day 02/028-alwaysblock2.md</x:v>
-      </x:c>
-      <x:c r="Q33" s="140" t="str">
-        <x:v>../../images/Day 02/028-alwaysblock2.png</x:v>
-      </x:c>
-      <x:c r="R33" s="140" t="str">
-        <x:v>../../solutions/Day 02/028-alwaysblock2.sv</x:v>
-      </x:c>
-      <x:c r="S33" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/alwaysblock2</x:v>
-      </x:c>
-      <x:c r="T33" s="141" t="str"/>
-    </x:row>
-    <x:row r="34" ht="34" customHeight="1">
+      <x:c r="P33" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/028-alwaysblock2.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/028-alwaysblock2.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q33" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/028-alwaysblock2.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/028-alwaysblock2.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R33" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/028-alwaysblock2.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/028-alwaysblock2.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S33" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/alwaysblock2","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/alwaysblock2, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T33" s="162" t="str">
+        <x:v>Describe clocked storage in an always block so the output captures the input on each active clock edge.</x:v>
+      </x:c>
+      <x:c r="U33" s="168"/>
+    </x:row>
+    <x:row r="34" ht="42" customHeight="1">
       <x:c r="A34" s="135" t="n">
         <x:v>29</x:v>
       </x:c>
@@ -3138,21 +3429,28 @@
       <x:c r="O34" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P34" s="140" t="str">
-        <x:v>../../problems/Day 02/029-always_if.md</x:v>
-      </x:c>
-      <x:c r="Q34" s="140" t="str">
-        <x:v>../../images/Day 02/029-always_if.png</x:v>
-      </x:c>
-      <x:c r="R34" s="140" t="str">
-        <x:v>../../solutions/Day 02/029-always_if.sv</x:v>
-      </x:c>
-      <x:c r="S34" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/always_if</x:v>
-      </x:c>
-      <x:c r="T34" s="141" t="str"/>
-    </x:row>
-    <x:row r="35" ht="34" customHeight="1">
+      <x:c r="P34" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/029-always_if.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/029-always_if.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q34" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/029-always_if.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/029-always_if.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R34" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/029-always_if.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/029-always_if.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S34" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/always_if","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_if, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T34" s="162" t="str">
+        <x:v>Use an if/else statement in combinational logic to implement the requested multiplexer behaviour.</x:v>
+      </x:c>
+      <x:c r="U34" s="168"/>
+    </x:row>
+    <x:row r="35" ht="42" customHeight="1">
       <x:c r="A35" s="135" t="n">
         <x:v>30</x:v>
       </x:c>
@@ -3196,21 +3494,28 @@
       <x:c r="O35" s="139" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="P35" s="140" t="str">
-        <x:v>../../problems/Day 02/030-always_if2.md</x:v>
-      </x:c>
-      <x:c r="Q35" s="140" t="str">
-        <x:v>../../images/Day 02/030-always_if2.png</x:v>
-      </x:c>
-      <x:c r="R35" s="140" t="str">
-        <x:v>../../solutions/Day 02/030-always_if2.sv</x:v>
-      </x:c>
-      <x:c r="S35" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/always_if2</x:v>
-      </x:c>
-      <x:c r="T35" s="141" t="str"/>
-    </x:row>
-    <x:row r="36" ht="34" customHeight="1">
+      <x:c r="P35" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/030-always_if2.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/030-always_if2.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q35" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/030-always_if2.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/030-always_if2.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R35" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/030-always_if2.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/030-always_if2.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S35" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/always_if2","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_if2, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T35" s="162" t="str">
+        <x:v>Correct an incomplete combinational if statement by assigning every output on every path and thereby avoiding latches.</x:v>
+      </x:c>
+      <x:c r="U35" s="168"/>
+    </x:row>
+    <x:row r="36" ht="42" customHeight="1">
       <x:c r="A36" s="135" t="n">
         <x:v>31</x:v>
       </x:c>
@@ -3254,21 +3559,28 @@
       <x:c r="O36" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P36" s="140" t="str">
-        <x:v>../../problems/Day 02/031-always_case.md</x:v>
-      </x:c>
-      <x:c r="Q36" s="140" t="str">
-        <x:v>../../images/Day 02/031-always_case.png</x:v>
-      </x:c>
-      <x:c r="R36" s="140" t="str">
-        <x:v>../../solutions/Day 02/031-always_case.sv</x:v>
-      </x:c>
-      <x:c r="S36" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/always_case</x:v>
-      </x:c>
-      <x:c r="T36" s="141" t="str"/>
-    </x:row>
-    <x:row r="37" ht="34" customHeight="1">
+      <x:c r="P36" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/031-always_case.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/031-always_case.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q36" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/031-always_case.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/031-always_case.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R36" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/031-always_case.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/031-always_case.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S36" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/always_case","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_case, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T36" s="162" t="str">
+        <x:v>Use a case statement to select one of several input values according to the selector.</x:v>
+      </x:c>
+      <x:c r="U36" s="168"/>
+    </x:row>
+    <x:row r="37" ht="42" customHeight="1">
       <x:c r="A37" s="135" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -3312,21 +3624,28 @@
       <x:c r="O37" s="139" t="n">
         <x:v>0.07</x:v>
       </x:c>
-      <x:c r="P37" s="140" t="str">
-        <x:v>../../problems/Day 02/032-always_case2.md</x:v>
-      </x:c>
-      <x:c r="Q37" s="140" t="str">
-        <x:v>../../images/Day 02/032-always_case2.png</x:v>
-      </x:c>
-      <x:c r="R37" s="140" t="str">
-        <x:v>../../solutions/Day 02/032-always_case2.sv</x:v>
-      </x:c>
-      <x:c r="S37" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/always_case2</x:v>
-      </x:c>
-      <x:c r="T37" s="141" t="str"/>
-    </x:row>
-    <x:row r="38" ht="34" customHeight="1">
+      <x:c r="P37" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/032-always_case2.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/032-always_case2.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q37" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/032-always_case2.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/032-always_case2.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R37" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/032-always_case2.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/032-always_case2.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S37" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/always_case2","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_case2, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T37" s="162" t="str">
+        <x:v>Implement a priority encoder whose output identifies the highest-priority asserted input bit.</x:v>
+      </x:c>
+      <x:c r="U37" s="168"/>
+    </x:row>
+    <x:row r="38" ht="42" customHeight="1">
       <x:c r="A38" s="135" t="n">
         <x:v>33</x:v>
       </x:c>
@@ -3370,21 +3689,28 @@
       <x:c r="O38" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P38" s="140" t="str">
-        <x:v>../../problems/Day 02/033-always_casez.md</x:v>
-      </x:c>
-      <x:c r="Q38" s="140" t="str">
-        <x:v>../../images/Day 02/033-always_casez.png</x:v>
-      </x:c>
-      <x:c r="R38" s="140" t="str">
-        <x:v>../../solutions/Day 02/033-always_casez.sv</x:v>
-      </x:c>
-      <x:c r="S38" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/always_casez</x:v>
-      </x:c>
-      <x:c r="T38" s="141" t="str"/>
-    </x:row>
-    <x:row r="39" ht="34" customHeight="1">
+      <x:c r="P38" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/033-always_casez.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/033-always_casez.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q38" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/033-always_casez.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/033-always_casez.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R38" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/033-always_casez.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/033-always_casez.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S38" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/always_casez","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_casez, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T38" s="162" t="str">
+        <x:v>Implement the priority encoder compactly with casez patterns and don't-care bits.</x:v>
+      </x:c>
+      <x:c r="U38" s="168"/>
+    </x:row>
+    <x:row r="39" ht="42" customHeight="1">
       <x:c r="A39" s="135" t="n">
         <x:v>34</x:v>
       </x:c>
@@ -3428,21 +3754,28 @@
       <x:c r="O39" s="139" t="n">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P39" s="140" t="str">
-        <x:v>../../problems/Day 02/034-always_nolatches.md</x:v>
-      </x:c>
-      <x:c r="Q39" s="140" t="str">
-        <x:v>../../images/Day 02/034-always_nolatches.png</x:v>
-      </x:c>
-      <x:c r="R39" s="140" t="str">
-        <x:v>../../solutions/Day 02/034-always_nolatches.sv</x:v>
-      </x:c>
-      <x:c r="S39" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/always_nolatches</x:v>
-      </x:c>
-      <x:c r="T39" s="141" t="str"/>
-    </x:row>
-    <x:row r="40" ht="34" customHeight="1">
+      <x:c r="P39" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/034-always_nolatches.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/034-always_nolatches.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q39" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/034-always_nolatches.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/034-always_nolatches.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R39" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/034-always_nolatches.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/034-always_nolatches.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S39" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/always_nolatches","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_nolatches, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T39" s="162" t="str">
+        <x:v>Complete the combinational case logic with safe defaults so no output retains an old value or infers a latch.</x:v>
+      </x:c>
+      <x:c r="U39" s="168"/>
+    </x:row>
+    <x:row r="40" ht="42" customHeight="1">
       <x:c r="A40" s="135" t="n">
         <x:v>35</x:v>
       </x:c>
@@ -3486,21 +3819,28 @@
       <x:c r="O40" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P40" s="140" t="str">
-        <x:v>../../problems/Day 02/035-conditional.md</x:v>
-      </x:c>
-      <x:c r="Q40" s="140" t="str">
-        <x:v>../../images/Day 02/035-conditional.png</x:v>
-      </x:c>
-      <x:c r="R40" s="140" t="str">
-        <x:v>../../solutions/Day 02/035-conditional.sv</x:v>
-      </x:c>
-      <x:c r="S40" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/conditional</x:v>
-      </x:c>
-      <x:c r="T40" s="141" t="str"/>
-    </x:row>
-    <x:row r="41" ht="34" customHeight="1">
+      <x:c r="P40" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/035-conditional.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/035-conditional.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q40" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/035-conditional.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/035-conditional.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R40" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/035-conditional.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/035-conditional.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S40" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/conditional","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/conditional, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T40" s="162" t="str">
+        <x:v>Use nested ternary operators to select the smallest unsigned value from several inputs.</x:v>
+      </x:c>
+      <x:c r="U40" s="168"/>
+    </x:row>
+    <x:row r="41" ht="42" customHeight="1">
       <x:c r="A41" s="135" t="n">
         <x:v>36</x:v>
       </x:c>
@@ -3544,21 +3884,28 @@
       <x:c r="O41" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P41" s="140" t="str">
-        <x:v>../../problems/Day 02/036-reduction.md</x:v>
-      </x:c>
-      <x:c r="Q41" s="140" t="str">
-        <x:v>../../images/Day 02/036-reduction.png</x:v>
-      </x:c>
-      <x:c r="R41" s="140" t="str">
-        <x:v>../../solutions/Day 02/036-reduction.sv</x:v>
-      </x:c>
-      <x:c r="S41" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/reduction</x:v>
-      </x:c>
-      <x:c r="T41" s="141" t="str"/>
-    </x:row>
-    <x:row r="42" ht="34" customHeight="1">
+      <x:c r="P41" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/036-reduction.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/036-reduction.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q41" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/036-reduction.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/036-reduction.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R41" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/036-reduction.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/036-reduction.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S41" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/reduction","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/reduction, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T41" s="162" t="str">
+        <x:v>Compare bitwise and reduction operators by producing per-bit results and single-bit reductions from two vectors.</x:v>
+      </x:c>
+      <x:c r="U41" s="168"/>
+    </x:row>
+    <x:row r="42" ht="42" customHeight="1">
       <x:c r="A42" s="135" t="n">
         <x:v>37</x:v>
       </x:c>
@@ -3602,21 +3949,28 @@
       <x:c r="O42" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P42" s="140" t="str">
-        <x:v>../../problems/Day 02/037-gates100.md</x:v>
-      </x:c>
-      <x:c r="Q42" s="140" t="str">
-        <x:v>../../images/Day 02/037-gates100.png</x:v>
-      </x:c>
-      <x:c r="R42" s="140" t="str">
-        <x:v>../../solutions/Day 02/037-gates100.sv</x:v>
-      </x:c>
-      <x:c r="S42" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/gates100</x:v>
-      </x:c>
-      <x:c r="T42" s="141" t="str"/>
-    </x:row>
-    <x:row r="43" ht="34" customHeight="1">
+      <x:c r="P42" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/037-gates100.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/037-gates100.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q42" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/037-gates100.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/037-gates100.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R42" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/037-gates100.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/037-gates100.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S42" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/gates100","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gates100, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T42" s="162" t="str">
+        <x:v>Apply reduction operators across a 100-bit vector to implement very wide AND, OR, and XOR gates.</x:v>
+      </x:c>
+      <x:c r="U42" s="168"/>
+    </x:row>
+    <x:row r="43" ht="42" customHeight="1">
       <x:c r="A43" s="135" t="n">
         <x:v>38</x:v>
       </x:c>
@@ -3660,21 +4014,28 @@
       <x:c r="O43" s="139" t="n">
         <x:v>0.38</x:v>
       </x:c>
-      <x:c r="P43" s="140" t="str">
-        <x:v>../../problems/Day 02/038-vector100r.md</x:v>
-      </x:c>
-      <x:c r="Q43" s="140" t="str">
-        <x:v>../../images/Day 02/038-vector100r.png</x:v>
-      </x:c>
-      <x:c r="R43" s="140" t="str">
-        <x:v>../../solutions/Day 02/038-vector100r.sv</x:v>
-      </x:c>
-      <x:c r="S43" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/vector100r</x:v>
-      </x:c>
-      <x:c r="T43" s="141" t="str"/>
-    </x:row>
-    <x:row r="44" ht="34" customHeight="1">
+      <x:c r="P43" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/038-vector100r.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/038-vector100r.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q43" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/038-vector100r.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/038-vector100r.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R43" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/038-vector100r.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/038-vector100r.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S43" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vector100r","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector100r, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T43" s="162" t="str">
+        <x:v>Use a combinational for loop to reverse all 100 bits of a vector.</x:v>
+      </x:c>
+      <x:c r="U43" s="168"/>
+    </x:row>
+    <x:row r="44" ht="42" customHeight="1">
       <x:c r="A44" s="135" t="n">
         <x:v>39</x:v>
       </x:c>
@@ -3718,21 +4079,28 @@
       <x:c r="O44" s="139" t="n">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="P44" s="140" t="str">
-        <x:v>../../problems/Day 02/039-popcount255.md</x:v>
-      </x:c>
-      <x:c r="Q44" s="140" t="str">
-        <x:v>../../images/Day 02/039-popcount255.png</x:v>
-      </x:c>
-      <x:c r="R44" s="140" t="str">
-        <x:v>../../solutions/Day 02/039-popcount255.sv</x:v>
-      </x:c>
-      <x:c r="S44" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/popcount255</x:v>
-      </x:c>
-      <x:c r="T44" s="141" t="str"/>
-    </x:row>
-    <x:row r="45" ht="34" customHeight="1">
+      <x:c r="P44" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/039-popcount255.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/039-popcount255.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q44" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/039-popcount255.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/039-popcount255.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R44" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/039-popcount255.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/039-popcount255.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S44" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/popcount255","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/popcount255, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T44" s="162" t="str">
+        <x:v>Count how many bits are high in a 255-bit input vector using combinational accumulation.</x:v>
+      </x:c>
+      <x:c r="U44" s="168"/>
+    </x:row>
+    <x:row r="45" ht="42" customHeight="1">
       <x:c r="A45" s="135" t="n">
         <x:v>40</x:v>
       </x:c>
@@ -3776,21 +4144,28 @@
       <x:c r="O45" s="139" t="n">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="P45" s="140" t="str">
-        <x:v>../../problems/Day 02/040-adder100i.md</x:v>
-      </x:c>
-      <x:c r="Q45" s="140" t="str">
-        <x:v>../../images/Day 02/040-adder100i.png</x:v>
-      </x:c>
-      <x:c r="R45" s="140" t="str">
-        <x:v>../../solutions/Day 02/040-adder100i.sv</x:v>
-      </x:c>
-      <x:c r="S45" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/adder100i</x:v>
-      </x:c>
-      <x:c r="T45" s="141" t="str"/>
-    </x:row>
-    <x:row r="46" ht="34" customHeight="1">
+      <x:c r="P45" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/040-adder100i.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/040-adder100i.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q45" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/040-adder100i.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/040-adder100i.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R45" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/040-adder100i.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/040-adder100i.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S45" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/adder100i","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/adder100i, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T45" s="162" t="str">
+        <x:v>Generate a 100-bit ripple-carry adder and return both the sum and the carry from every bit stage.</x:v>
+      </x:c>
+      <x:c r="U45" s="168"/>
+    </x:row>
+    <x:row r="46" ht="42" customHeight="1">
       <x:c r="A46" s="135" t="n">
         <x:v>41</x:v>
       </x:c>
@@ -3834,21 +4209,28 @@
       <x:c r="O46" s="139" t="n">
         <x:v>0.17</x:v>
       </x:c>
-      <x:c r="P46" s="140" t="str">
-        <x:v>../../problems/Day 03/041-bcdadd100.md</x:v>
-      </x:c>
-      <x:c r="Q46" s="140" t="str">
-        <x:v>../../images/Day 03/041-bcdadd100.png</x:v>
-      </x:c>
-      <x:c r="R46" s="140" t="str">
-        <x:v>../../solutions/Day 03/041-bcdadd100.sv</x:v>
-      </x:c>
-      <x:c r="S46" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/bcdadd100</x:v>
-      </x:c>
-      <x:c r="T46" s="141" t="str"/>
-    </x:row>
-    <x:row r="47" ht="34" customHeight="1">
+      <x:c r="P46" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/041-bcdadd100.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/041-bcdadd100.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q46" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/041-bcdadd100.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/041-bcdadd100.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R46" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/041-bcdadd100.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/041-bcdadd100.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S46" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/bcdadd100","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bcdadd100, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T46" s="162" t="str">
+        <x:v>Chain 100 one-digit BCD adders to add two 100-digit decimal numbers with carry propagation.</x:v>
+      </x:c>
+      <x:c r="U46" s="168"/>
+    </x:row>
+    <x:row r="47" ht="42" customHeight="1">
       <x:c r="A47" s="135" t="n">
         <x:v>42</x:v>
       </x:c>
@@ -3894,21 +4276,28 @@
       <x:c r="O47" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P47" s="140" t="str">
-        <x:v>../../problems/Day 02/042-exams__m2014_q4h.md</x:v>
-      </x:c>
-      <x:c r="Q47" s="140" t="str">
-        <x:v>../../images/Day 02/042-exams__m2014_q4h.png</x:v>
-      </x:c>
-      <x:c r="R47" s="140" t="str">
-        <x:v>../../solutions/Day 02/042-exams__m2014_q4h.sv</x:v>
-      </x:c>
-      <x:c r="S47" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/m2014_q4h</x:v>
-      </x:c>
-      <x:c r="T47" s="141" t="str"/>
-    </x:row>
-    <x:row r="48" ht="34" customHeight="1">
+      <x:c r="P47" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/042-exams__m2014_q4h.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/042-exams__m2014_q4h.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q47" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/042-exams__m2014_q4h.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/042-exams__m2014_q4h.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R47" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/042-exams__m2014_q4h.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/042-exams__m2014_q4h.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S47" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4h","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4h, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T47" s="162" t="str">
+        <x:v>Implement the shown circuit's output as a direct wire connection.</x:v>
+      </x:c>
+      <x:c r="U47" s="168"/>
+    </x:row>
+    <x:row r="48" ht="42" customHeight="1">
       <x:c r="A48" s="135" t="n">
         <x:v>43</x:v>
       </x:c>
@@ -3954,21 +4343,28 @@
       <x:c r="O48" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P48" s="140" t="str">
-        <x:v>../../problems/Day 02/043-exams__m2014_q4i.md</x:v>
-      </x:c>
-      <x:c r="Q48" s="140" t="str">
-        <x:v>../../images/Day 02/043-exams__m2014_q4i.png</x:v>
-      </x:c>
-      <x:c r="R48" s="140" t="str">
-        <x:v>../../solutions/Day 02/043-exams__m2014_q4i.sv</x:v>
-      </x:c>
-      <x:c r="S48" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/m2014_q4i</x:v>
-      </x:c>
-      <x:c r="T48" s="141" t="str"/>
-    </x:row>
-    <x:row r="49" ht="34" customHeight="1">
+      <x:c r="P48" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/043-exams__m2014_q4i.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/043-exams__m2014_q4i.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q48" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/043-exams__m2014_q4i.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/043-exams__m2014_q4i.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R48" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/043-exams__m2014_q4i.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/043-exams__m2014_q4i.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S48" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4i","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4i, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T48" s="162" t="str">
+        <x:v>Tie the requested output permanently low to represent ground.</x:v>
+      </x:c>
+      <x:c r="U48" s="168"/>
+    </x:row>
+    <x:row r="49" ht="42" customHeight="1">
       <x:c r="A49" s="135" t="n">
         <x:v>44</x:v>
       </x:c>
@@ -4014,21 +4410,28 @@
       <x:c r="O49" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P49" s="140" t="str">
-        <x:v>../../problems/Day 02/044-exams__m2014_q4e.md</x:v>
-      </x:c>
-      <x:c r="Q49" s="140" t="str">
-        <x:v>../../images/Day 02/044-exams__m2014_q4e.png</x:v>
-      </x:c>
-      <x:c r="R49" s="140" t="str">
-        <x:v>../../solutions/Day 02/044-exams__m2014_q4e.sv</x:v>
-      </x:c>
-      <x:c r="S49" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/m2014_q4e</x:v>
-      </x:c>
-      <x:c r="T49" s="141" t="str"/>
-    </x:row>
-    <x:row r="50" ht="34" customHeight="1">
+      <x:c r="P49" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/044-exams__m2014_q4e.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/044-exams__m2014_q4e.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q49" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/044-exams__m2014_q4e.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/044-exams__m2014_q4e.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R49" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/044-exams__m2014_q4e.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/044-exams__m2014_q4e.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S49" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4e","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4e, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T49" s="162" t="str">
+        <x:v>Translate the shown gate symbol into the equivalent NOR logic expression.</x:v>
+      </x:c>
+      <x:c r="U49" s="168"/>
+    </x:row>
+    <x:row r="50" ht="42" customHeight="1">
       <x:c r="A50" s="135" t="n">
         <x:v>45</x:v>
       </x:c>
@@ -4074,21 +4477,28 @@
       <x:c r="O50" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P50" s="140" t="str">
-        <x:v>../../problems/Day 02/045-exams__m2014_q4f.md</x:v>
-      </x:c>
-      <x:c r="Q50" s="140" t="str">
-        <x:v>../../images/Day 02/045-exams__m2014_q4f.png</x:v>
-      </x:c>
-      <x:c r="R50" s="140" t="str">
-        <x:v>../../solutions/Day 02/045-exams__m2014_q4f.sv</x:v>
-      </x:c>
-      <x:c r="S50" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/m2014_q4f</x:v>
-      </x:c>
-      <x:c r="T50" s="141" t="str"/>
-    </x:row>
-    <x:row r="51" ht="34" customHeight="1">
+      <x:c r="P50" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/045-exams__m2014_q4f.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/045-exams__m2014_q4f.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q50" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/045-exams__m2014_q4f.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/045-exams__m2014_q4f.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R50" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/045-exams__m2014_q4f.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/045-exams__m2014_q4f.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S50" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4f","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4f, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T50" s="162" t="str">
+        <x:v>Identify the function of the shown gate circuit and express it correctly in Verilog.</x:v>
+      </x:c>
+      <x:c r="U50" s="168"/>
+    </x:row>
+    <x:row r="51" ht="42" customHeight="1">
       <x:c r="A51" s="135" t="n">
         <x:v>46</x:v>
       </x:c>
@@ -4134,21 +4544,28 @@
       <x:c r="O51" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P51" s="140" t="str">
-        <x:v>../../problems/Day 02/046-exams__m2014_q4g.md</x:v>
-      </x:c>
-      <x:c r="Q51" s="140" t="str">
-        <x:v>../../images/Day 02/046-exams__m2014_q4g.png</x:v>
-      </x:c>
-      <x:c r="R51" s="140" t="str">
-        <x:v>../../solutions/Day 02/046-exams__m2014_q4g.sv</x:v>
-      </x:c>
-      <x:c r="S51" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/m2014_q4g</x:v>
-      </x:c>
-      <x:c r="T51" s="141" t="str"/>
-    </x:row>
-    <x:row r="52" ht="34" customHeight="1">
+      <x:c r="P51" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/046-exams__m2014_q4g.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/046-exams__m2014_q4g.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q51" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/046-exams__m2014_q4g.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/046-exams__m2014_q4g.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R51" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/046-exams__m2014_q4g.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/046-exams__m2014_q4g.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S51" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4g","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4g, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T51" s="162" t="str">
+        <x:v>Translate the two-gate schematic into a single correct combinational output expression.</x:v>
+      </x:c>
+      <x:c r="U51" s="168"/>
+    </x:row>
+    <x:row r="52" ht="42" customHeight="1">
       <x:c r="A52" s="135" t="n">
         <x:v>47</x:v>
       </x:c>
@@ -4194,21 +4611,28 @@
       <x:c r="O52" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P52" s="140" t="str">
-        <x:v>../../problems/Day 03/047-gates.md</x:v>
-      </x:c>
-      <x:c r="Q52" s="140" t="str">
-        <x:v>../../images/Day 03/047-gates.png</x:v>
-      </x:c>
-      <x:c r="R52" s="140" t="str">
-        <x:v>../../solutions/Day 03/047-gates.sv</x:v>
-      </x:c>
-      <x:c r="S52" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/gates</x:v>
-      </x:c>
-      <x:c r="T52" s="141" t="str"/>
-    </x:row>
-    <x:row r="53" ht="34" customHeight="1">
+      <x:c r="P52" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/047-gates.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/047-gates.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q52" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/047-gates.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/047-gates.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R52" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/047-gates.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/047-gates.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S52" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/gates","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gates, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T52" s="162" t="str">
+        <x:v>Implement several basic gates at once, including bitwise outputs and their logical complements.</x:v>
+      </x:c>
+      <x:c r="U52" s="168"/>
+    </x:row>
+    <x:row r="53" ht="42" customHeight="1">
       <x:c r="A53" s="135" t="n">
         <x:v>48</x:v>
       </x:c>
@@ -4254,21 +4678,28 @@
       <x:c r="O53" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P53" s="140" t="str">
-        <x:v>../../problems/Day 03/048-7420.md</x:v>
-      </x:c>
-      <x:c r="Q53" s="140" t="str">
-        <x:v>../../images/Day 03/048-7420.png</x:v>
-      </x:c>
-      <x:c r="R53" s="140" t="str">
-        <x:v>../../solutions/Day 03/048-7420.sv</x:v>
-      </x:c>
-      <x:c r="S53" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/7420</x:v>
-      </x:c>
-      <x:c r="T53" s="141" t="str"/>
-    </x:row>
-    <x:row r="54" ht="34" customHeight="1">
+      <x:c r="P53" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/048-7420.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/048-7420.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q53" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/048-7420.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/048-7420.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R53" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/048-7420.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/048-7420.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S53" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/7420","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/7420, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T53" s="162" t="str">
+        <x:v>Model a 7420 chip containing two independent four-input NAND gates.</x:v>
+      </x:c>
+      <x:c r="U53" s="168"/>
+    </x:row>
+    <x:row r="54" ht="42" customHeight="1">
       <x:c r="A54" s="135" t="n">
         <x:v>49</x:v>
       </x:c>
@@ -4314,21 +4745,28 @@
       <x:c r="O54" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P54" s="140" t="str">
-        <x:v>../../problems/Day 03/049-truthtable1.md</x:v>
-      </x:c>
-      <x:c r="Q54" s="140" t="str">
-        <x:v>../../images/Day 03/049-truthtable1.png</x:v>
-      </x:c>
-      <x:c r="R54" s="140" t="str">
-        <x:v>../../solutions/Day 03/049-truthtable1.sv</x:v>
-      </x:c>
-      <x:c r="S54" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/truthtable1</x:v>
-      </x:c>
-      <x:c r="T54" s="141" t="str"/>
-    </x:row>
-    <x:row r="55" ht="34" customHeight="1">
+      <x:c r="P54" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/049-truthtable1.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/049-truthtable1.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q54" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/049-truthtable1.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/049-truthtable1.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R54" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/049-truthtable1.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/049-truthtable1.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S54" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/truthtable1","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/truthtable1, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T54" s="162" t="str">
+        <x:v>Convert the supplied truth table into combinational Verilog that produces the specified output for every input combination.</x:v>
+      </x:c>
+      <x:c r="U54" s="168"/>
+    </x:row>
+    <x:row r="55" ht="42" customHeight="1">
       <x:c r="A55" s="135" t="n">
         <x:v>50</x:v>
       </x:c>
@@ -4374,21 +4812,28 @@
       <x:c r="O55" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P55" s="140" t="str">
-        <x:v>../../problems/Day 03/050-mt2015_eq2.md</x:v>
-      </x:c>
-      <x:c r="Q55" s="140" t="str">
-        <x:v>../../images/Day 03/050-mt2015_eq2.png</x:v>
-      </x:c>
-      <x:c r="R55" s="140" t="str">
-        <x:v>../../solutions/Day 03/050-mt2015_eq2.sv</x:v>
-      </x:c>
-      <x:c r="S55" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/mt2015_eq2</x:v>
-      </x:c>
-      <x:c r="T55" s="141" t="str"/>
-    </x:row>
-    <x:row r="56" ht="34" customHeight="1">
+      <x:c r="P55" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/050-mt2015_eq2.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/050-mt2015_eq2.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q55" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/050-mt2015_eq2.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/050-mt2015_eq2.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R55" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/050-mt2015_eq2.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/050-mt2015_eq2.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S55" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mt2015_eq2","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_eq2, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T55" s="162" t="str">
+        <x:v>Compare two 2-bit inputs and assert the output only when both vectors are equal.</x:v>
+      </x:c>
+      <x:c r="U55" s="168"/>
+    </x:row>
+    <x:row r="56" ht="42" customHeight="1">
       <x:c r="A56" s="135" t="n">
         <x:v>51</x:v>
       </x:c>
@@ -4434,21 +4879,28 @@
       <x:c r="O56" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P56" s="140" t="str">
-        <x:v>../../problems/Day 03/051-mt2015_q4a.md</x:v>
-      </x:c>
-      <x:c r="Q56" s="140" t="str">
-        <x:v>../../images/Day 03/051-mt2015_q4a.png</x:v>
-      </x:c>
-      <x:c r="R56" s="140" t="str">
-        <x:v>../../solutions/Day 03/051-mt2015_q4a.sv</x:v>
-      </x:c>
-      <x:c r="S56" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/mt2015_q4a</x:v>
-      </x:c>
-      <x:c r="T56" s="141" t="str"/>
-    </x:row>
-    <x:row r="57" ht="34" customHeight="1">
+      <x:c r="P56" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/051-mt2015_q4a.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/051-mt2015_q4a.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q56" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/051-mt2015_q4a.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/051-mt2015_q4a.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R56" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/051-mt2015_q4a.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/051-mt2015_q4a.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S56" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mt2015_q4a","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_q4a, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T56" s="162" t="str">
+        <x:v>Implement the first small combinational circuit exactly as shown in the diagram.</x:v>
+      </x:c>
+      <x:c r="U56" s="168"/>
+    </x:row>
+    <x:row r="57" ht="42" customHeight="1">
       <x:c r="A57" s="135" t="n">
         <x:v>52</x:v>
       </x:c>
@@ -4494,21 +4946,28 @@
       <x:c r="O57" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P57" s="140" t="str">
-        <x:v>../../problems/Day 03/052-mt2015_q4b.md</x:v>
-      </x:c>
-      <x:c r="Q57" s="140" t="str">
-        <x:v>../../images/Day 03/052-mt2015_q4b.png</x:v>
-      </x:c>
-      <x:c r="R57" s="140" t="str">
-        <x:v>../../solutions/Day 03/052-mt2015_q4b.sv</x:v>
-      </x:c>
-      <x:c r="S57" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/mt2015_q4b</x:v>
-      </x:c>
-      <x:c r="T57" s="141" t="str"/>
-    </x:row>
-    <x:row r="58" ht="34" customHeight="1">
+      <x:c r="P57" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/052-mt2015_q4b.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/052-mt2015_q4b.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q57" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/052-mt2015_q4b.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/052-mt2015_q4b.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R57" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/052-mt2015_q4b.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/052-mt2015_q4b.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S57" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mt2015_q4b","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_q4b, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T57" s="162" t="str">
+        <x:v>Implement the second small combinational circuit exactly as shown in the diagram.</x:v>
+      </x:c>
+      <x:c r="U57" s="168"/>
+    </x:row>
+    <x:row r="58" ht="42" customHeight="1">
       <x:c r="A58" s="135" t="n">
         <x:v>53</x:v>
       </x:c>
@@ -4554,21 +5013,28 @@
       <x:c r="O58" s="139" t="n">
         <x:v>0.14</x:v>
       </x:c>
-      <x:c r="P58" s="140" t="str">
-        <x:v>../../problems/Day 03/053-mt2015_q4.md</x:v>
-      </x:c>
-      <x:c r="Q58" s="140" t="str">
-        <x:v>../../images/Day 03/053-mt2015_q4.png</x:v>
-      </x:c>
-      <x:c r="R58" s="140" t="str">
-        <x:v>../../solutions/Day 03/053-mt2015_q4.sv</x:v>
-      </x:c>
-      <x:c r="S58" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/mt2015_q4</x:v>
-      </x:c>
-      <x:c r="T58" s="141" t="str"/>
-    </x:row>
-    <x:row r="59" ht="34" customHeight="1">
+      <x:c r="P58" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/053-mt2015_q4.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/053-mt2015_q4.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q58" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/053-mt2015_q4.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/053-mt2015_q4.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R58" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/053-mt2015_q4.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/053-mt2015_q4.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S58" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mt2015_q4","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_q4, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T58" s="162" t="str">
+        <x:v>Instantiate or combine circuits A and B so they operate together with the requested top-level connections.</x:v>
+      </x:c>
+      <x:c r="U58" s="168"/>
+    </x:row>
+    <x:row r="59" ht="42" customHeight="1">
       <x:c r="A59" s="135" t="n">
         <x:v>54</x:v>
       </x:c>
@@ -4614,21 +5080,28 @@
       <x:c r="O59" s="139" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P59" s="140" t="str">
-        <x:v>../../problems/Day 03/054-ringer.md</x:v>
-      </x:c>
-      <x:c r="Q59" s="140" t="str">
-        <x:v>../../images/Day 03/054-ringer.png</x:v>
-      </x:c>
-      <x:c r="R59" s="140" t="str">
-        <x:v>../../solutions/Day 03/054-ringer.sv</x:v>
-      </x:c>
-      <x:c r="S59" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/ringer</x:v>
-      </x:c>
-      <x:c r="T59" s="141" t="str"/>
-    </x:row>
-    <x:row r="60" ht="34" customHeight="1">
+      <x:c r="P59" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/054-ringer.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/054-ringer.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q59" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/054-ringer.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/054-ringer.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R59" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/054-ringer.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/054-ringer.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S59" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/ringer","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/ringer, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T59" s="162" t="str">
+        <x:v>Choose whether a phone should ring or vibrate from the incoming-call and silent-mode control signals.</x:v>
+      </x:c>
+      <x:c r="U59" s="168"/>
+    </x:row>
+    <x:row r="60" ht="42" customHeight="1">
       <x:c r="A60" s="135" t="n">
         <x:v>55</x:v>
       </x:c>
@@ -4674,21 +5147,28 @@
       <x:c r="O60" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P60" s="140" t="str">
-        <x:v>../../problems/Day 03/055-thermostat.md</x:v>
-      </x:c>
-      <x:c r="Q60" s="140" t="str">
-        <x:v>../../images/Day 03/055-thermostat.png</x:v>
-      </x:c>
-      <x:c r="R60" s="140" t="str">
-        <x:v>../../solutions/Day 03/055-thermostat.sv</x:v>
-      </x:c>
-      <x:c r="S60" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/thermostat</x:v>
-      </x:c>
-      <x:c r="T60" s="141" t="str"/>
-    </x:row>
-    <x:row r="61" ht="34" customHeight="1">
+      <x:c r="P60" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/055-thermostat.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/055-thermostat.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q60" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/055-thermostat.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/055-thermostat.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R60" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/055-thermostat.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/055-thermostat.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S60" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/thermostat","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/thermostat, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T60" s="162" t="str">
+        <x:v>Implement the thermostat's heater, air-conditioner, and fan control rules from the temperature and mode inputs.</x:v>
+      </x:c>
+      <x:c r="U60" s="168"/>
+    </x:row>
+    <x:row r="61" ht="42" customHeight="1">
       <x:c r="A61" s="135" t="n">
         <x:v>56</x:v>
       </x:c>
@@ -4734,21 +5214,28 @@
       <x:c r="O61" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P61" s="140" t="str">
-        <x:v>../../problems/Day 03/056-popcount3.md</x:v>
-      </x:c>
-      <x:c r="Q61" s="140" t="str">
-        <x:v>../../images/Day 03/056-popcount3.png</x:v>
-      </x:c>
-      <x:c r="R61" s="140" t="str">
-        <x:v>../../solutions/Day 03/056-popcount3.sv</x:v>
-      </x:c>
-      <x:c r="S61" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/popcount3</x:v>
-      </x:c>
-      <x:c r="T61" s="141" t="str"/>
-    </x:row>
-    <x:row r="62" ht="34" customHeight="1">
+      <x:c r="P61" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/056-popcount3.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/056-popcount3.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q61" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/056-popcount3.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/056-popcount3.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R61" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/056-popcount3.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/056-popcount3.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S61" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/popcount3","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/popcount3, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T61" s="162" t="str">
+        <x:v>Count the number of asserted bits in a 3-bit input and return that count as a binary value.</x:v>
+      </x:c>
+      <x:c r="U61" s="168"/>
+    </x:row>
+    <x:row r="62" ht="42" customHeight="1">
       <x:c r="A62" s="135" t="n">
         <x:v>57</x:v>
       </x:c>
@@ -4794,21 +5281,28 @@
       <x:c r="O62" s="139" t="n">
         <x:v>0.17</x:v>
       </x:c>
-      <x:c r="P62" s="140" t="str">
-        <x:v>../../problems/Day 03/057-gatesv.md</x:v>
-      </x:c>
-      <x:c r="Q62" s="140" t="str">
-        <x:v>../../images/Day 03/057-gatesv.png</x:v>
-      </x:c>
-      <x:c r="R62" s="140" t="str">
-        <x:v>../../solutions/Day 03/057-gatesv.sv</x:v>
-      </x:c>
-      <x:c r="S62" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/gatesv</x:v>
-      </x:c>
-      <x:c r="T62" s="141" t="str"/>
-    </x:row>
-    <x:row r="63" ht="34" customHeight="1">
+      <x:c r="P62" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/057-gatesv.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/057-gatesv.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q62" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/057-gatesv.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/057-gatesv.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R62" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/057-gatesv.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/057-gatesv.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S62" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/gatesv","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gatesv, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T62" s="162" t="str">
+        <x:v>For two vectors, compute bitwise gate results and also indicate whether the vectors differ at any or every position.</x:v>
+      </x:c>
+      <x:c r="U62" s="168"/>
+    </x:row>
+    <x:row r="63" ht="42" customHeight="1">
       <x:c r="A63" s="135" t="n">
         <x:v>58</x:v>
       </x:c>
@@ -4854,21 +5348,28 @@
       <x:c r="O63" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P63" s="140" t="str">
-        <x:v>../../problems/Day 03/058-gatesv100.md</x:v>
-      </x:c>
-      <x:c r="Q63" s="140" t="str">
-        <x:v>../../images/Day 03/058-gatesv100.png</x:v>
-      </x:c>
-      <x:c r="R63" s="140" t="str">
-        <x:v>../../solutions/Day 03/058-gatesv100.sv</x:v>
-      </x:c>
-      <x:c r="S63" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/gatesv100</x:v>
-      </x:c>
-      <x:c r="T63" s="141" t="str"/>
-    </x:row>
-    <x:row r="64" ht="34" customHeight="1">
+      <x:c r="P63" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/058-gatesv100.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/058-gatesv100.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q63" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/058-gatesv100.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/058-gatesv100.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R63" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/058-gatesv100.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/058-gatesv100.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S63" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/gatesv100","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gatesv100, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T63" s="162" t="str">
+        <x:v>Extend the vector-gate comparison to 100-bit inputs, including per-bit outputs and wide reduction results.</x:v>
+      </x:c>
+      <x:c r="U63" s="168"/>
+    </x:row>
+    <x:row r="64" ht="42" customHeight="1">
       <x:c r="A64" s="135" t="n">
         <x:v>59</x:v>
       </x:c>
@@ -4914,21 +5415,28 @@
       <x:c r="O64" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P64" s="140" t="str">
-        <x:v>../../problems/Day 03/059-mux2to1.md</x:v>
-      </x:c>
-      <x:c r="Q64" s="140" t="str">
-        <x:v>../../images/Day 03/059-mux2to1.png</x:v>
-      </x:c>
-      <x:c r="R64" s="140" t="str">
-        <x:v>../../solutions/Day 03/059-mux2to1.sv</x:v>
-      </x:c>
-      <x:c r="S64" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/mux2to1</x:v>
-      </x:c>
-      <x:c r="T64" s="141" t="str"/>
-    </x:row>
-    <x:row r="65" ht="34" customHeight="1">
+      <x:c r="P64" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/059-mux2to1.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/059-mux2to1.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q64" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/059-mux2to1.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/059-mux2to1.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R64" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/059-mux2to1.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/059-mux2to1.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S64" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mux2to1","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux2to1, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T64" s="162" t="str">
+        <x:v>Implement a one-bit 2-to-1 multiplexer that selects one input according to the select signal.</x:v>
+      </x:c>
+      <x:c r="U64" s="168"/>
+    </x:row>
+    <x:row r="65" ht="42" customHeight="1">
       <x:c r="A65" s="135" t="n">
         <x:v>60</x:v>
       </x:c>
@@ -4974,21 +5482,28 @@
       <x:c r="O65" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P65" s="140" t="str">
-        <x:v>../../problems/Day 03/060-mux2to1v.md</x:v>
-      </x:c>
-      <x:c r="Q65" s="140" t="str">
-        <x:v>../../images/Day 03/060-mux2to1v.png</x:v>
-      </x:c>
-      <x:c r="R65" s="140" t="str">
-        <x:v>../../solutions/Day 03/060-mux2to1v.sv</x:v>
-      </x:c>
-      <x:c r="S65" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/mux2to1v</x:v>
-      </x:c>
-      <x:c r="T65" s="141" t="str"/>
-    </x:row>
-    <x:row r="66" ht="34" customHeight="1">
+      <x:c r="P65" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/060-mux2to1v.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/060-mux2to1v.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q65" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/060-mux2to1v.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/060-mux2to1v.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R65" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/060-mux2to1v.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/060-mux2to1v.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S65" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mux2to1v","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux2to1v, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T65" s="162" t="str">
+        <x:v>Implement a 2-to-1 multiplexer that selects an entire vector rather than a single bit.</x:v>
+      </x:c>
+      <x:c r="U65" s="168"/>
+    </x:row>
+    <x:row r="66" ht="42" customHeight="1">
       <x:c r="A66" s="135" t="n">
         <x:v>61</x:v>
       </x:c>
@@ -5034,21 +5549,28 @@
       <x:c r="O66" s="139" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="P66" s="140" t="str">
-        <x:v>../../problems/Day 03/061-mux9to1v.md</x:v>
-      </x:c>
-      <x:c r="Q66" s="140" t="str">
-        <x:v>../../images/Day 03/061-mux9to1v.png</x:v>
-      </x:c>
-      <x:c r="R66" s="140" t="str">
-        <x:v>../../solutions/Day 03/061-mux9to1v.sv</x:v>
-      </x:c>
-      <x:c r="S66" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/mux9to1v</x:v>
-      </x:c>
-      <x:c r="T66" s="141" t="str"/>
-    </x:row>
-    <x:row r="67" ht="34" customHeight="1">
+      <x:c r="P66" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/061-mux9to1v.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/061-mux9to1v.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q66" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/061-mux9to1v.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/061-mux9to1v.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R66" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/061-mux9to1v.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/061-mux9to1v.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S66" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mux9to1v","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux9to1v, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T66" s="162" t="str">
+        <x:v>Select one of nine 16-bit inputs; produce the required default value when the selector is outside the valid range.</x:v>
+      </x:c>
+      <x:c r="U66" s="168"/>
+    </x:row>
+    <x:row r="67" ht="42" customHeight="1">
       <x:c r="A67" s="135" t="n">
         <x:v>62</x:v>
       </x:c>
@@ -5094,21 +5616,28 @@
       <x:c r="O67" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P67" s="140" t="str">
-        <x:v>../../problems/Day 03/062-mux256to1.md</x:v>
-      </x:c>
-      <x:c r="Q67" s="140" t="str">
-        <x:v>../../images/Day 03/062-mux256to1.png</x:v>
-      </x:c>
-      <x:c r="R67" s="140" t="str">
-        <x:v>../../solutions/Day 03/062-mux256to1.sv</x:v>
-      </x:c>
-      <x:c r="S67" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/mux256to1</x:v>
-      </x:c>
-      <x:c r="T67" s="141" t="str"/>
-    </x:row>
-    <x:row r="68" ht="34" customHeight="1">
+      <x:c r="P67" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/062-mux256to1.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/062-mux256to1.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q67" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/062-mux256to1.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/062-mux256to1.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R67" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/062-mux256to1.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/062-mux256to1.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S67" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mux256to1","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux256to1, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T67" s="162" t="str">
+        <x:v>Select one bit from a 256-bit input vector using an 8-bit selector as the index.</x:v>
+      </x:c>
+      <x:c r="U67" s="168"/>
+    </x:row>
+    <x:row r="68" ht="42" customHeight="1">
       <x:c r="A68" s="135" t="n">
         <x:v>63</x:v>
       </x:c>
@@ -5154,21 +5683,28 @@
       <x:c r="O68" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P68" s="140" t="str">
-        <x:v>../../problems/Day 03/063-mux256to1v.md</x:v>
-      </x:c>
-      <x:c r="Q68" s="140" t="str">
-        <x:v>../../images/Day 03/063-mux256to1v.png</x:v>
-      </x:c>
-      <x:c r="R68" s="140" t="str">
-        <x:v>../../solutions/Day 03/063-mux256to1v.sv</x:v>
-      </x:c>
-      <x:c r="S68" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/mux256to1v</x:v>
-      </x:c>
-      <x:c r="T68" s="141" t="str"/>
-    </x:row>
-    <x:row r="69" ht="34" customHeight="1">
+      <x:c r="P68" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/063-mux256to1v.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/063-mux256to1v.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q68" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/063-mux256to1v.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/063-mux256to1v.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R68" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/063-mux256to1v.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/063-mux256to1v.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S68" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mux256to1v","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux256to1v, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T68" s="162" t="str">
+        <x:v>Select one 4-bit word from 256 packed words by calculating the correct vector slice from the selector.</x:v>
+      </x:c>
+      <x:c r="U68" s="168"/>
+    </x:row>
+    <x:row r="69" ht="42" customHeight="1">
       <x:c r="A69" s="135" t="n">
         <x:v>64</x:v>
       </x:c>
@@ -5214,21 +5750,28 @@
       <x:c r="O69" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P69" s="140" t="str">
-        <x:v>../../problems/Day 03/064-hadd.md</x:v>
-      </x:c>
-      <x:c r="Q69" s="140" t="str">
-        <x:v>../../images/Day 03/064-hadd.png</x:v>
-      </x:c>
-      <x:c r="R69" s="140" t="str">
-        <x:v>../../solutions/Day 03/064-hadd.sv</x:v>
-      </x:c>
-      <x:c r="S69" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/hadd</x:v>
-      </x:c>
-      <x:c r="T69" s="141" t="str"/>
-    </x:row>
-    <x:row r="70" ht="34" customHeight="1">
+      <x:c r="P69" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/064-hadd.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/064-hadd.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q69" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/064-hadd.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/064-hadd.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R69" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/064-hadd.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/064-hadd.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S69" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/hadd","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/hadd, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T69" s="162" t="str">
+        <x:v>Implement a half adder that produces a one-bit sum and carry from two input bits.</x:v>
+      </x:c>
+      <x:c r="U69" s="168"/>
+    </x:row>
+    <x:row r="70" ht="42" customHeight="1">
       <x:c r="A70" s="135" t="n">
         <x:v>65</x:v>
       </x:c>
@@ -5274,21 +5817,28 @@
       <x:c r="O70" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P70" s="140" t="str">
-        <x:v>../../problems/Day 02/065-fadd.md</x:v>
-      </x:c>
-      <x:c r="Q70" s="140" t="str">
-        <x:v>../../images/Day 02/065-fadd.png</x:v>
-      </x:c>
-      <x:c r="R70" s="140" t="str">
-        <x:v>../../solutions/Day 02/065-fadd.sv</x:v>
-      </x:c>
-      <x:c r="S70" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/fadd</x:v>
-      </x:c>
-      <x:c r="T70" s="141" t="str"/>
-    </x:row>
-    <x:row r="71" ht="34" customHeight="1">
+      <x:c r="P70" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/065-fadd.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2002/065-fadd.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q70" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/065-fadd.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2002/065-fadd.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R70" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/065-fadd.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2002/065-fadd.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S70" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fadd","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fadd, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T70" s="162" t="str">
+        <x:v>Implement a full adder that includes carry-in and produces both sum and carry-out.</x:v>
+      </x:c>
+      <x:c r="U70" s="168"/>
+    </x:row>
+    <x:row r="71" ht="42" customHeight="1">
       <x:c r="A71" s="135" t="n">
         <x:v>66</x:v>
       </x:c>
@@ -5334,21 +5884,28 @@
       <x:c r="O71" s="139" t="n">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P71" s="140" t="str">
-        <x:v>../../problems/Day 03/066-adder3.md</x:v>
-      </x:c>
-      <x:c r="Q71" s="140" t="str">
-        <x:v>../../images/Day 03/066-adder3.png</x:v>
-      </x:c>
-      <x:c r="R71" s="140" t="str">
-        <x:v>../../solutions/Day 03/066-adder3.sv</x:v>
-      </x:c>
-      <x:c r="S71" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/adder3</x:v>
-      </x:c>
-      <x:c r="T71" s="141" t="str"/>
-    </x:row>
-    <x:row r="72" ht="34" customHeight="1">
+      <x:c r="P71" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/066-adder3.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/066-adder3.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q71" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/066-adder3.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/066-adder3.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R71" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/066-adder3.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/066-adder3.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S71" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/adder3","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/adder3, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T71" s="162" t="str">
+        <x:v>Chain three full adders to add two 3-bit numbers and expose the intermediate carry signals.</x:v>
+      </x:c>
+      <x:c r="U71" s="168"/>
+    </x:row>
+    <x:row r="72" ht="42" customHeight="1">
       <x:c r="A72" s="135" t="n">
         <x:v>67</x:v>
       </x:c>
@@ -5394,21 +5951,28 @@
       <x:c r="O72" s="139" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P72" s="140" t="str">
-        <x:v>../../problems/Day 03/067-exams__m2014_q4j.md</x:v>
-      </x:c>
-      <x:c r="Q72" s="140" t="str">
-        <x:v>../../images/Day 03/067-exams__m2014_q4j.png</x:v>
-      </x:c>
-      <x:c r="R72" s="140" t="str">
-        <x:v>../../solutions/Day 03/067-exams__m2014_q4j.sv</x:v>
-      </x:c>
-      <x:c r="S72" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/m2014_q4j</x:v>
-      </x:c>
-      <x:c r="T72" s="141" t="str"/>
-    </x:row>
-    <x:row r="73" ht="34" customHeight="1">
+      <x:c r="P72" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/067-exams__m2014_q4j.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/067-exams__m2014_q4j.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q72" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/067-exams__m2014_q4j.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/067-exams__m2014_q4j.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R72" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/067-exams__m2014_q4j.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/067-exams__m2014_q4j.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S72" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4j","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4j, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T72" s="162" t="str">
+        <x:v>Implement the adder circuit shown in the exam diagram with the requested sum and carry behaviour.</x:v>
+      </x:c>
+      <x:c r="U72" s="168"/>
+    </x:row>
+    <x:row r="73" ht="42" customHeight="1">
       <x:c r="A73" s="135" t="n">
         <x:v>68</x:v>
       </x:c>
@@ -5454,21 +6018,28 @@
       <x:c r="O73" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P73" s="140" t="str">
-        <x:v>../../problems/Day 03/068-exams__ece241_2014_q1c.md</x:v>
-      </x:c>
-      <x:c r="Q73" s="140" t="str">
-        <x:v>../../images/Day 03/068-exams__ece241_2014_q1c.png</x:v>
-      </x:c>
-      <x:c r="R73" s="140" t="str">
-        <x:v>../../solutions/Day 03/068-exams__ece241_2014_q1c.sv</x:v>
-      </x:c>
-      <x:c r="S73" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/ece241_2014_q1c</x:v>
-      </x:c>
-      <x:c r="T73" s="141" t="str"/>
-    </x:row>
-    <x:row r="74" ht="34" customHeight="1">
+      <x:c r="P73" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/068-exams__ece241_2014_q1c.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/068-exams__ece241_2014_q1c.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q73" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/068-exams__ece241_2014_q1c.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/068-exams__ece241_2014_q1c.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R73" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/068-exams__ece241_2014_q1c.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/068-exams__ece241_2014_q1c.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S73" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2014_q1c","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q1c, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T73" s="162" t="str">
+        <x:v>Add two signed values and assert overflow when the mathematical result cannot fit in the signed output width.</x:v>
+      </x:c>
+      <x:c r="U73" s="168"/>
+    </x:row>
+    <x:row r="74" ht="42" customHeight="1">
       <x:c r="A74" s="135" t="n">
         <x:v>69</x:v>
       </x:c>
@@ -5514,21 +6085,28 @@
       <x:c r="O74" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P74" s="140" t="str">
-        <x:v>../../problems/Day 03/069-adder100.md</x:v>
-      </x:c>
-      <x:c r="Q74" s="140" t="str">
-        <x:v>../../images/Day 03/069-adder100.png</x:v>
-      </x:c>
-      <x:c r="R74" s="140" t="str">
-        <x:v>../../solutions/Day 03/069-adder100.sv</x:v>
-      </x:c>
-      <x:c r="S74" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/adder100</x:v>
-      </x:c>
-      <x:c r="T74" s="141" t="str"/>
-    </x:row>
-    <x:row r="75" ht="34" customHeight="1">
+      <x:c r="P74" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/069-adder100.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/069-adder100.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q74" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/069-adder100.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/069-adder100.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R74" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/069-adder100.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/069-adder100.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S74" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/adder100","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/adder100, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T74" s="162" t="str">
+        <x:v>Implement a 100-bit combinational adder and return the final carry-out together with the sum.</x:v>
+      </x:c>
+      <x:c r="U74" s="168"/>
+    </x:row>
+    <x:row r="75" ht="42" customHeight="1">
       <x:c r="A75" s="135" t="n">
         <x:v>70</x:v>
       </x:c>
@@ -5574,21 +6152,28 @@
       <x:c r="O75" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P75" s="140" t="str">
-        <x:v>../../problems/Day 03/070-bcdadd4.md</x:v>
-      </x:c>
-      <x:c r="Q75" s="140" t="str">
-        <x:v>../../images/Day 03/070-bcdadd4.png</x:v>
-      </x:c>
-      <x:c r="R75" s="140" t="str">
-        <x:v>../../solutions/Day 03/070-bcdadd4.sv</x:v>
-      </x:c>
-      <x:c r="S75" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/bcdadd4</x:v>
-      </x:c>
-      <x:c r="T75" s="141" t="str"/>
-    </x:row>
-    <x:row r="76" ht="34" customHeight="1">
+      <x:c r="P75" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/070-bcdadd4.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/070-bcdadd4.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q75" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/070-bcdadd4.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/070-bcdadd4.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R75" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/070-bcdadd4.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/070-bcdadd4.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S75" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/bcdadd4","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bcdadd4, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T75" s="162" t="str">
+        <x:v>Chain four BCD full adders to add two four-digit decimal values and propagate decimal carry between digits.</x:v>
+      </x:c>
+      <x:c r="U75" s="168"/>
+    </x:row>
+    <x:row r="76" ht="42" customHeight="1">
       <x:c r="A76" s="135" t="n">
         <x:v>71</x:v>
       </x:c>
@@ -5634,21 +6219,28 @@
       <x:c r="O76" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P76" s="140" t="str">
-        <x:v>../../problems/Day 03/071-kmap1.md</x:v>
-      </x:c>
-      <x:c r="Q76" s="140" t="str">
-        <x:v>../../images/Day 03/071-kmap1.png</x:v>
-      </x:c>
-      <x:c r="R76" s="140" t="str">
-        <x:v>../../solutions/Day 03/071-kmap1.sv</x:v>
-      </x:c>
-      <x:c r="S76" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/kmap1</x:v>
-      </x:c>
-      <x:c r="T76" s="141" t="str"/>
-    </x:row>
-    <x:row r="77" ht="34" customHeight="1">
+      <x:c r="P76" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/071-kmap1.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/071-kmap1.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q76" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/071-kmap1.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/071-kmap1.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R76" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/071-kmap1.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/071-kmap1.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S76" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/kmap1","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/kmap1, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T76" s="162" t="str">
+        <x:v>Derive and implement the simplified logic function represented by the supplied 3-variable Karnaugh map.</x:v>
+      </x:c>
+      <x:c r="U76" s="168"/>
+    </x:row>
+    <x:row r="77" ht="42" customHeight="1">
       <x:c r="A77" s="135" t="n">
         <x:v>72</x:v>
       </x:c>
@@ -5694,21 +6286,28 @@
       <x:c r="O77" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P77" s="140" t="str">
-        <x:v>../../problems/Day 03/072-kmap2.md</x:v>
-      </x:c>
-      <x:c r="Q77" s="140" t="str">
-        <x:v>../../images/Day 03/072-kmap2.png</x:v>
-      </x:c>
-      <x:c r="R77" s="140" t="str">
-        <x:v>../../solutions/Day 03/072-kmap2.sv</x:v>
-      </x:c>
-      <x:c r="S77" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/kmap2</x:v>
-      </x:c>
-      <x:c r="T77" s="141" t="str"/>
-    </x:row>
-    <x:row r="78" ht="34" customHeight="1">
+      <x:c r="P77" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/072-kmap2.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/072-kmap2.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q77" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/072-kmap2.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/072-kmap2.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R77" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/072-kmap2.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/072-kmap2.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S77" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/kmap2","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/kmap2, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T77" s="162" t="str">
+        <x:v>Derive a minimal combinational expression from the supplied 4-variable Karnaugh map.</x:v>
+      </x:c>
+      <x:c r="U77" s="168"/>
+    </x:row>
+    <x:row r="78" ht="42" customHeight="1">
       <x:c r="A78" s="135" t="n">
         <x:v>73</x:v>
       </x:c>
@@ -5754,21 +6353,28 @@
       <x:c r="O78" s="139" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P78" s="140" t="str">
-        <x:v>../../problems/Day 03/073-kmap3.md</x:v>
-      </x:c>
-      <x:c r="Q78" s="140" t="str">
-        <x:v>../../images/Day 03/073-kmap3.png</x:v>
-      </x:c>
-      <x:c r="R78" s="140" t="str">
-        <x:v>../../solutions/Day 03/073-kmap3.sv</x:v>
-      </x:c>
-      <x:c r="S78" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/kmap3</x:v>
-      </x:c>
-      <x:c r="T78" s="141" t="str"/>
-    </x:row>
-    <x:row r="79" ht="34" customHeight="1">
+      <x:c r="P78" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/073-kmap3.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/073-kmap3.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q78" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/073-kmap3.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/073-kmap3.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R78" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/073-kmap3.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/073-kmap3.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S78" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/kmap3","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/kmap3, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T78" s="162" t="str">
+        <x:v>Implement the 4-variable Karnaugh-map function while using the indicated don't-care cells for simplification.</x:v>
+      </x:c>
+      <x:c r="U78" s="168"/>
+    </x:row>
+    <x:row r="79" ht="42" customHeight="1">
       <x:c r="A79" s="135" t="n">
         <x:v>74</x:v>
       </x:c>
@@ -5814,21 +6420,28 @@
       <x:c r="O79" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P79" s="140" t="str">
-        <x:v>../../problems/Day 03/074-kmap4.md</x:v>
-      </x:c>
-      <x:c r="Q79" s="140" t="str">
-        <x:v>../../images/Day 03/074-kmap4.png</x:v>
-      </x:c>
-      <x:c r="R79" s="140" t="str">
-        <x:v>../../solutions/Day 03/074-kmap4.sv</x:v>
-      </x:c>
-      <x:c r="S79" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/kmap4</x:v>
-      </x:c>
-      <x:c r="T79" s="141" t="str"/>
-    </x:row>
-    <x:row r="80" ht="34" customHeight="1">
+      <x:c r="P79" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/074-kmap4.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/074-kmap4.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q79" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/074-kmap4.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/074-kmap4.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R79" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/074-kmap4.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/074-kmap4.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S79" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/kmap4","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/kmap4, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T79" s="162" t="str">
+        <x:v>Translate the supplied 4-variable Karnaugh map into a correct simplified Verilog expression.</x:v>
+      </x:c>
+      <x:c r="U79" s="168"/>
+    </x:row>
+    <x:row r="80" ht="42" customHeight="1">
       <x:c r="A80" s="135" t="n">
         <x:v>75</x:v>
       </x:c>
@@ -5874,21 +6487,28 @@
       <x:c r="O80" s="139" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P80" s="140" t="str">
-        <x:v>../../problems/Day 03/075-exams__ece241_2013_q2.md</x:v>
-      </x:c>
-      <x:c r="Q80" s="140" t="str">
-        <x:v>../../images/Day 03/075-exams__ece241_2013_q2.png</x:v>
-      </x:c>
-      <x:c r="R80" s="140" t="str">
-        <x:v>../../solutions/Day 03/075-exams__ece241_2013_q2.sv</x:v>
-      </x:c>
-      <x:c r="S80" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/ece241_2013_q2</x:v>
-      </x:c>
-      <x:c r="T80" s="141" t="str"/>
-    </x:row>
-    <x:row r="81" ht="34" customHeight="1">
+      <x:c r="P80" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/075-exams__ece241_2013_q2.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/075-exams__ece241_2013_q2.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q80" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/075-exams__ece241_2013_q2.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/075-exams__ece241_2013_q2.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R80" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/075-exams__ece241_2013_q2.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/075-exams__ece241_2013_q2.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S80" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2013_q2","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2013_q2, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T80" s="162" t="str">
+        <x:v>Implement both the minimum sum-of-products and minimum product-of-sums forms for the given logic function.</x:v>
+      </x:c>
+      <x:c r="U80" s="168"/>
+    </x:row>
+    <x:row r="81" ht="42" customHeight="1">
       <x:c r="A81" s="135" t="n">
         <x:v>76</x:v>
       </x:c>
@@ -5934,21 +6554,28 @@
       <x:c r="O81" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P81" s="140" t="str">
-        <x:v>../../problems/Day 03/076-exams__m2014_q3.md</x:v>
-      </x:c>
-      <x:c r="Q81" s="140" t="str">
-        <x:v>../../images/Day 03/076-exams__m2014_q3.png</x:v>
-      </x:c>
-      <x:c r="R81" s="140" t="str">
-        <x:v>../../solutions/Day 03/076-exams__m2014_q3.sv</x:v>
-      </x:c>
-      <x:c r="S81" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/m2014_q3</x:v>
-      </x:c>
-      <x:c r="T81" s="141" t="str"/>
-    </x:row>
-    <x:row r="82" ht="34" customHeight="1">
+      <x:c r="P81" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/076-exams__m2014_q3.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/076-exams__m2014_q3.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q81" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/076-exams__m2014_q3.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/076-exams__m2014_q3.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R81" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/076-exams__m2014_q3.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/076-exams__m2014_q3.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S81" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q3","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q3, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T81" s="162" t="str">
+        <x:v>Simplify the exam Karnaugh map and implement the resulting combinational output.</x:v>
+      </x:c>
+      <x:c r="U81" s="168"/>
+    </x:row>
+    <x:row r="82" ht="42" customHeight="1">
       <x:c r="A82" s="135" t="n">
         <x:v>77</x:v>
       </x:c>
@@ -5994,21 +6621,28 @@
       <x:c r="O82" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P82" s="140" t="str">
-        <x:v>../../problems/Day 03/077-exams__2012_q1g.md</x:v>
-      </x:c>
-      <x:c r="Q82" s="140" t="str">
-        <x:v>../../images/Day 03/077-exams__2012_q1g.png</x:v>
-      </x:c>
-      <x:c r="R82" s="140" t="str">
-        <x:v>../../solutions/Day 03/077-exams__2012_q1g.sv</x:v>
-      </x:c>
-      <x:c r="S82" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/2012_q1g</x:v>
-      </x:c>
-      <x:c r="T82" s="141" t="str"/>
-    </x:row>
-    <x:row r="83" ht="34" customHeight="1">
+      <x:c r="P82" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/077-exams__2012_q1g.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/077-exams__2012_q1g.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q82" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/077-exams__2012_q1g.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/077-exams__2012_q1g.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R82" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/077-exams__2012_q1g.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/077-exams__2012_q1g.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S82" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2012_q1g","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2012_q1g, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T82" s="162" t="str">
+        <x:v>Convert the supplied Karnaugh map, including any don't-care conditions, into simplified logic.</x:v>
+      </x:c>
+      <x:c r="U82" s="168"/>
+    </x:row>
+    <x:row r="83" ht="42" customHeight="1">
       <x:c r="A83" s="135" t="n">
         <x:v>78</x:v>
       </x:c>
@@ -6054,21 +6688,28 @@
       <x:c r="O83" s="139" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P83" s="140" t="str">
-        <x:v>../../problems/Day 03/078-exams__ece241_2014_q3.md</x:v>
-      </x:c>
-      <x:c r="Q83" s="140" t="str">
-        <x:v>../../images/Day 03/078-exams__ece241_2014_q3.png</x:v>
-      </x:c>
-      <x:c r="R83" s="140" t="str">
-        <x:v>../../solutions/Day 03/078-exams__ece241_2014_q3.sv</x:v>
-      </x:c>
-      <x:c r="S83" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/ece241_2014_q3</x:v>
-      </x:c>
-      <x:c r="T83" s="141" t="str"/>
-    </x:row>
-    <x:row r="84" ht="34" customHeight="1">
+      <x:c r="P83" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/078-exams__ece241_2014_q3.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/078-exams__ece241_2014_q3.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q83" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/078-exams__ece241_2014_q3.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/078-exams__ece241_2014_q3.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R83" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/078-exams__ece241_2014_q3.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/078-exams__ece241_2014_q3.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S83" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2014_q3","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q3, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T83" s="162" t="str">
+        <x:v>Implement the Karnaugh-map function using the specified multiplexer structure and input assignments.</x:v>
+      </x:c>
+      <x:c r="U83" s="168"/>
+    </x:row>
+    <x:row r="84" ht="42" customHeight="1">
       <x:c r="A84" s="135" t="n">
         <x:v>79</x:v>
       </x:c>
@@ -6114,21 +6755,28 @@
       <x:c r="O84" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P84" s="140" t="str">
-        <x:v>../../problems/Day 03/079-dff.md</x:v>
-      </x:c>
-      <x:c r="Q84" s="140" t="str">
-        <x:v>../../images/Day 03/079-dff.png</x:v>
-      </x:c>
-      <x:c r="R84" s="140" t="str">
-        <x:v>../../solutions/Day 03/079-dff.sv</x:v>
-      </x:c>
-      <x:c r="S84" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/dff</x:v>
-      </x:c>
-      <x:c r="T84" s="141" t="str"/>
-    </x:row>
-    <x:row r="85" ht="34" customHeight="1">
+      <x:c r="P84" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/079-dff.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/079-dff.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q84" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/079-dff.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/079-dff.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R84" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/079-dff.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/079-dff.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S84" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/dff","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T84" s="162" t="str">
+        <x:v>Create a positive-edge-triggered D flip-flop that stores the input value on each rising clock edge.</x:v>
+      </x:c>
+      <x:c r="U84" s="168"/>
+    </x:row>
+    <x:row r="85" ht="42" customHeight="1">
       <x:c r="A85" s="135" t="n">
         <x:v>80</x:v>
       </x:c>
@@ -6174,21 +6822,28 @@
       <x:c r="O85" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P85" s="140" t="str">
-        <x:v>../../problems/Day 03/080-dff8.md</x:v>
-      </x:c>
-      <x:c r="Q85" s="140" t="str">
-        <x:v>../../images/Day 03/080-dff8.png</x:v>
-      </x:c>
-      <x:c r="R85" s="140" t="str">
-        <x:v>../../solutions/Day 03/080-dff8.sv</x:v>
-      </x:c>
-      <x:c r="S85" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/dff8</x:v>
-      </x:c>
-      <x:c r="T85" s="141" t="str"/>
-    </x:row>
-    <x:row r="86" ht="34" customHeight="1">
+      <x:c r="P85" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/080-dff8.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/080-dff8.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q85" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/080-dff8.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/080-dff8.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R85" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/080-dff8.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/080-dff8.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S85" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/dff8","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff8, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T85" s="162" t="str">
+        <x:v>Create eight D flip-flops in parallel so an entire 8-bit vector is registered on the rising clock edge.</x:v>
+      </x:c>
+      <x:c r="U85" s="168"/>
+    </x:row>
+    <x:row r="86" ht="42" customHeight="1">
       <x:c r="A86" s="135" t="n">
         <x:v>81</x:v>
       </x:c>
@@ -6234,21 +6889,28 @@
       <x:c r="O86" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P86" s="140" t="str">
-        <x:v>../../problems/Day 03/081-dff8r.md</x:v>
-      </x:c>
-      <x:c r="Q86" s="140" t="str">
-        <x:v>../../images/Day 03/081-dff8r.png</x:v>
-      </x:c>
-      <x:c r="R86" s="140" t="str">
-        <x:v>../../solutions/Day 03/081-dff8r.sv</x:v>
-      </x:c>
-      <x:c r="S86" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/dff8r</x:v>
-      </x:c>
-      <x:c r="T86" s="141" t="str"/>
-    </x:row>
-    <x:row r="87" ht="34" customHeight="1">
+      <x:c r="P86" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/081-dff8r.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/081-dff8r.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q86" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/081-dff8r.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/081-dff8r.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R86" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/081-dff8r.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/081-dff8r.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S86" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/dff8r","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff8r, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T86" s="162" t="str">
+        <x:v>Add a synchronous reset to an 8-bit register so reset is sampled on the active clock edge.</x:v>
+      </x:c>
+      <x:c r="U86" s="168"/>
+    </x:row>
+    <x:row r="87" ht="42" customHeight="1">
       <x:c r="A87" s="135" t="n">
         <x:v>82</x:v>
       </x:c>
@@ -6294,21 +6956,28 @@
       <x:c r="O87" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P87" s="140" t="str">
-        <x:v>../../problems/Day 03/082-dff8p.md</x:v>
-      </x:c>
-      <x:c r="Q87" s="140" t="str">
-        <x:v>../../images/Day 03/082-dff8p.png</x:v>
-      </x:c>
-      <x:c r="R87" s="140" t="str">
-        <x:v>../../solutions/Day 03/082-dff8p.sv</x:v>
-      </x:c>
-      <x:c r="S87" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/dff8p</x:v>
-      </x:c>
-      <x:c r="T87" s="141" t="str"/>
-    </x:row>
-    <x:row r="88" ht="34" customHeight="1">
+      <x:c r="P87" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/082-dff8p.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/082-dff8p.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q87" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/082-dff8p.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/082-dff8p.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R87" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/082-dff8p.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/082-dff8p.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S87" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/dff8p","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff8p, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T87" s="162" t="str">
+        <x:v>Create an 8-bit register whose synchronous reset loads the specified non-zero reset value.</x:v>
+      </x:c>
+      <x:c r="U87" s="168"/>
+    </x:row>
+    <x:row r="88" ht="42" customHeight="1">
       <x:c r="A88" s="135" t="n">
         <x:v>83</x:v>
       </x:c>
@@ -6354,21 +7023,28 @@
       <x:c r="O88" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P88" s="140" t="str">
-        <x:v>../../problems/Day 03/083-dff8ar.md</x:v>
-      </x:c>
-      <x:c r="Q88" s="140" t="str">
-        <x:v>../../images/Day 03/083-dff8ar.png</x:v>
-      </x:c>
-      <x:c r="R88" s="140" t="str">
-        <x:v>../../solutions/Day 03/083-dff8ar.sv</x:v>
-      </x:c>
-      <x:c r="S88" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/dff8ar</x:v>
-      </x:c>
-      <x:c r="T88" s="141" t="str"/>
-    </x:row>
-    <x:row r="89" ht="34" customHeight="1">
+      <x:c r="P88" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/083-dff8ar.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/083-dff8ar.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q88" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/083-dff8ar.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/083-dff8ar.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R88" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/083-dff8ar.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/083-dff8ar.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S88" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/dff8ar","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff8ar, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T88" s="162" t="str">
+        <x:v>Create an 8-bit register with asynchronous reset, allowing reset to change the output without waiting for a clock edge.</x:v>
+      </x:c>
+      <x:c r="U88" s="168"/>
+    </x:row>
+    <x:row r="89" ht="42" customHeight="1">
       <x:c r="A89" s="135" t="n">
         <x:v>84</x:v>
       </x:c>
@@ -6414,21 +7090,28 @@
       <x:c r="O89" s="139" t="n">
         <x:v>0.11</x:v>
       </x:c>
-      <x:c r="P89" s="140" t="str">
-        <x:v>../../problems/Day 03/084-dff16e.md</x:v>
-      </x:c>
-      <x:c r="Q89" s="140" t="str">
-        <x:v>../../images/Day 03/084-dff16e.png</x:v>
-      </x:c>
-      <x:c r="R89" s="140" t="str">
-        <x:v>../../solutions/Day 03/084-dff16e.sv</x:v>
-      </x:c>
-      <x:c r="S89" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/dff16e</x:v>
-      </x:c>
-      <x:c r="T89" s="141" t="str"/>
-    </x:row>
-    <x:row r="90" ht="34" customHeight="1">
+      <x:c r="P89" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/084-dff16e.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/084-dff16e.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q89" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/084-dff16e.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/084-dff16e.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R89" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/084-dff16e.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/084-dff16e.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S89" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/dff16e","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff16e, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T89" s="162" t="str">
+        <x:v>Build a 16-bit register with synchronous reset and independent byte-enable controls for its upper and lower bytes.</x:v>
+      </x:c>
+      <x:c r="U89" s="168"/>
+    </x:row>
+    <x:row r="90" ht="42" customHeight="1">
       <x:c r="A90" s="135" t="n">
         <x:v>85</x:v>
       </x:c>
@@ -6474,21 +7157,28 @@
       <x:c r="O90" s="139" t="n">
         <x:v>0.13</x:v>
       </x:c>
-      <x:c r="P90" s="140" t="str">
-        <x:v>../../problems/Day 03/085-exams__m2014_q4a.md</x:v>
-      </x:c>
-      <x:c r="Q90" s="140" t="str">
-        <x:v>../../images/Day 03/085-exams__m2014_q4a.png</x:v>
-      </x:c>
-      <x:c r="R90" s="140" t="str">
-        <x:v>../../solutions/Day 03/085-exams__m2014_q4a.sv</x:v>
-      </x:c>
-      <x:c r="S90" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/m2014_q4a</x:v>
-      </x:c>
-      <x:c r="T90" s="141" t="str"/>
-    </x:row>
-    <x:row r="91" ht="34" customHeight="1">
+      <x:c r="P90" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/085-exams__m2014_q4a.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/085-exams__m2014_q4a.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q90" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/085-exams__m2014_q4a.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/085-exams__m2014_q4a.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R90" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/085-exams__m2014_q4a.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/085-exams__m2014_q4a.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S90" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4a","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4a, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T90" s="162" t="str">
+        <x:v>Model the level-sensitive D latch shown in the exam circuit.</x:v>
+      </x:c>
+      <x:c r="U90" s="168"/>
+    </x:row>
+    <x:row r="91" ht="42" customHeight="1">
       <x:c r="A91" s="135" t="n">
         <x:v>86</x:v>
       </x:c>
@@ -6534,21 +7224,28 @@
       <x:c r="O91" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P91" s="140" t="str">
-        <x:v>../../problems/Day 03/086-exams__m2014_q4b.md</x:v>
-      </x:c>
-      <x:c r="Q91" s="140" t="str">
-        <x:v>../../images/Day 03/086-exams__m2014_q4b.png</x:v>
-      </x:c>
-      <x:c r="R91" s="140" t="str">
-        <x:v>../../solutions/Day 03/086-exams__m2014_q4b.sv</x:v>
-      </x:c>
-      <x:c r="S91" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/m2014_q4b</x:v>
-      </x:c>
-      <x:c r="T91" s="141" t="str"/>
-    </x:row>
-    <x:row r="92" ht="34" customHeight="1">
+      <x:c r="P91" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/086-exams__m2014_q4b.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/086-exams__m2014_q4b.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q91" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/086-exams__m2014_q4b.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/086-exams__m2014_q4b.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R91" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/086-exams__m2014_q4b.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/086-exams__m2014_q4b.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S91" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4b","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4b, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T91" s="162" t="str">
+        <x:v>Model the positive-edge-triggered D flip-flop shown in the exam circuit.</x:v>
+      </x:c>
+      <x:c r="U91" s="168"/>
+    </x:row>
+    <x:row r="92" ht="42" customHeight="1">
       <x:c r="A92" s="135" t="n">
         <x:v>87</x:v>
       </x:c>
@@ -6594,21 +7291,28 @@
       <x:c r="O92" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P92" s="140" t="str">
-        <x:v>../../problems/Day 03/087-exams__m2014_q4c.md</x:v>
-      </x:c>
-      <x:c r="Q92" s="140" t="str">
-        <x:v>../../images/Day 03/087-exams__m2014_q4c.png</x:v>
-      </x:c>
-      <x:c r="R92" s="140" t="str">
-        <x:v>../../solutions/Day 03/087-exams__m2014_q4c.sv</x:v>
-      </x:c>
-      <x:c r="S92" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/m2014_q4c</x:v>
-      </x:c>
-      <x:c r="T92" s="141" t="str"/>
-    </x:row>
-    <x:row r="93" ht="34" customHeight="1">
+      <x:c r="P92" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/087-exams__m2014_q4c.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/087-exams__m2014_q4c.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q92" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/087-exams__m2014_q4c.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/087-exams__m2014_q4c.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R92" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/087-exams__m2014_q4c.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/087-exams__m2014_q4c.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S92" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4c","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4c, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T92" s="162" t="str">
+        <x:v>Model the specified D flip-flop behaviour and its control connection from the diagram.</x:v>
+      </x:c>
+      <x:c r="U92" s="168"/>
+    </x:row>
+    <x:row r="93" ht="42" customHeight="1">
       <x:c r="A93" s="135" t="n">
         <x:v>88</x:v>
       </x:c>
@@ -6654,21 +7358,28 @@
       <x:c r="O93" s="139" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P93" s="140" t="str">
-        <x:v>../../problems/Day 03/088-exams__m2014_q4d.md</x:v>
-      </x:c>
-      <x:c r="Q93" s="140" t="str">
-        <x:v>../../images/Day 03/088-exams__m2014_q4d.png</x:v>
-      </x:c>
-      <x:c r="R93" s="140" t="str">
-        <x:v>../../solutions/Day 03/088-exams__m2014_q4d.sv</x:v>
-      </x:c>
-      <x:c r="S93" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/m2014_q4d</x:v>
-      </x:c>
-      <x:c r="T93" s="141" t="str"/>
-    </x:row>
-    <x:row r="94" ht="34" customHeight="1">
+      <x:c r="P93" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/088-exams__m2014_q4d.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2003/088-exams__m2014_q4d.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q93" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/088-exams__m2014_q4d.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2003/088-exams__m2014_q4d.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R93" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/088-exams__m2014_q4d.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2003/088-exams__m2014_q4d.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S93" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4d","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4d, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T93" s="162" t="str">
+        <x:v>Implement the shown combination of a D flip-flop and combinational gate.</x:v>
+      </x:c>
+      <x:c r="U93" s="168"/>
+    </x:row>
+    <x:row r="94" ht="42" customHeight="1">
       <x:c r="A94" s="135" t="n">
         <x:v>89</x:v>
       </x:c>
@@ -6714,21 +7425,28 @@
       <x:c r="O94" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P94" s="140" t="str">
-        <x:v>../../problems/Day 04/089-mt2015_muxdff.md</x:v>
-      </x:c>
-      <x:c r="Q94" s="140" t="str">
-        <x:v>../../images/Day 04/089-mt2015_muxdff.png</x:v>
-      </x:c>
-      <x:c r="R94" s="140" t="str">
-        <x:v>../../solutions/Day 04/089-mt2015_muxdff.sv</x:v>
-      </x:c>
-      <x:c r="S94" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/mt2015_muxdff</x:v>
-      </x:c>
-      <x:c r="T94" s="141" t="str"/>
-    </x:row>
-    <x:row r="95" ht="34" customHeight="1">
+      <x:c r="P94" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/089-mt2015_muxdff.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/089-mt2015_muxdff.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q94" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/089-mt2015_muxdff.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/089-mt2015_muxdff.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R94" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/089-mt2015_muxdff.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/089-mt2015_muxdff.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S94" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mt2015_muxdff","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_muxdff, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T94" s="162" t="str">
+        <x:v>Implement the circuit in which a multiplexer chooses the value captured by a D flip-flop.</x:v>
+      </x:c>
+      <x:c r="U94" s="168"/>
+    </x:row>
+    <x:row r="95" ht="42" customHeight="1">
       <x:c r="A95" s="135" t="n">
         <x:v>90</x:v>
       </x:c>
@@ -6774,21 +7492,28 @@
       <x:c r="O95" s="139" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P95" s="140" t="str">
-        <x:v>../../problems/Day 04/090-exams__2014_q4a.md</x:v>
-      </x:c>
-      <x:c r="Q95" s="140" t="str">
-        <x:v>../../images/Day 04/090-exams__2014_q4a.png</x:v>
-      </x:c>
-      <x:c r="R95" s="140" t="str">
-        <x:v>../../solutions/Day 04/090-exams__2014_q4a.sv</x:v>
-      </x:c>
-      <x:c r="S95" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/2014_q4a</x:v>
-      </x:c>
-      <x:c r="T95" s="141" t="str"/>
-    </x:row>
-    <x:row r="96" ht="34" customHeight="1">
+      <x:c r="P95" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/090-exams__2014_q4a.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/090-exams__2014_q4a.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q95" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/090-exams__2014_q4a.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/090-exams__2014_q4a.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R95" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/090-exams__2014_q4a.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/090-exams__2014_q4a.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S95" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2014_q4a","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2014_q4a, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T95" s="162" t="str">
+        <x:v>Translate the exam's multiplexer-and-DFF schematic into equivalent sequential Verilog.</x:v>
+      </x:c>
+      <x:c r="U95" s="168"/>
+    </x:row>
+    <x:row r="96" ht="42" customHeight="1">
       <x:c r="A96" s="135" t="n">
         <x:v>91</x:v>
       </x:c>
@@ -6834,21 +7559,28 @@
       <x:c r="O96" s="139" t="n">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P96" s="140" t="str">
-        <x:v>../../problems/Day 04/091-exams__ece241_2014_q4.md</x:v>
-      </x:c>
-      <x:c r="Q96" s="140" t="str">
-        <x:v>../../images/Day 04/091-exams__ece241_2014_q4.png</x:v>
-      </x:c>
-      <x:c r="R96" s="140" t="str">
-        <x:v>../../solutions/Day 04/091-exams__ece241_2014_q4.sv</x:v>
-      </x:c>
-      <x:c r="S96" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/ece241_2014_q4</x:v>
-      </x:c>
-      <x:c r="T96" s="141" t="str"/>
-    </x:row>
-    <x:row r="97" ht="34" customHeight="1">
+      <x:c r="P96" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/091-exams__ece241_2014_q4.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/091-exams__ece241_2014_q4.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q96" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/091-exams__ece241_2014_q4.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/091-exams__ece241_2014_q4.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R96" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/091-exams__ece241_2014_q4.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/091-exams__ece241_2014_q4.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S96" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2014_q4","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q4, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T96" s="162" t="str">
+        <x:v>Implement the shown network of D flip-flops and logic gates with the correct cycle-to-cycle behaviour.</x:v>
+      </x:c>
+      <x:c r="U96" s="168"/>
+    </x:row>
+    <x:row r="97" ht="42" customHeight="1">
       <x:c r="A97" s="135" t="n">
         <x:v>92</x:v>
       </x:c>
@@ -6894,21 +7626,28 @@
       <x:c r="O97" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P97" s="140" t="str">
-        <x:v>../../problems/Day 04/092-exams__ece241_2013_q7.md</x:v>
-      </x:c>
-      <x:c r="Q97" s="140" t="str">
-        <x:v>../../images/Day 04/092-exams__ece241_2013_q7.png</x:v>
-      </x:c>
-      <x:c r="R97" s="140" t="str">
-        <x:v>../../solutions/Day 04/092-exams__ece241_2013_q7.sv</x:v>
-      </x:c>
-      <x:c r="S97" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/ece241_2013_q7</x:v>
-      </x:c>
-      <x:c r="T97" s="141" t="str"/>
-    </x:row>
-    <x:row r="98" ht="34" customHeight="1">
+      <x:c r="P97" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/092-exams__ece241_2013_q7.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/092-exams__ece241_2013_q7.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q97" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/092-exams__ece241_2013_q7.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/092-exams__ece241_2013_q7.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R97" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/092-exams__ece241_2013_q7.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/092-exams__ece241_2013_q7.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S97" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2013_q7","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2013_q7, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T97" s="162" t="str">
+        <x:v>Build the sequential circuit described by the state/output truth table, including its registered state.</x:v>
+      </x:c>
+      <x:c r="U97" s="168"/>
+    </x:row>
+    <x:row r="98" ht="42" customHeight="1">
       <x:c r="A98" s="135" t="n">
         <x:v>93</x:v>
       </x:c>
@@ -6954,21 +7693,28 @@
       <x:c r="O98" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P98" s="140" t="str">
-        <x:v>../../problems/Day 04/093-edgedetect.md</x:v>
-      </x:c>
-      <x:c r="Q98" s="140" t="str">
-        <x:v>../../images/Day 04/093-edgedetect.png</x:v>
-      </x:c>
-      <x:c r="R98" s="140" t="str">
-        <x:v>../../solutions/Day 04/093-edgedetect.sv</x:v>
-      </x:c>
-      <x:c r="S98" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/edgedetect</x:v>
-      </x:c>
-      <x:c r="T98" s="141" t="str"/>
-    </x:row>
-    <x:row r="99" ht="34" customHeight="1">
+      <x:c r="P98" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/093-edgedetect.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/093-edgedetect.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q98" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/093-edgedetect.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/093-edgedetect.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R98" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/093-edgedetect.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/093-edgedetect.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S98" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/edgedetect","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/edgedetect, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T98" s="162" t="str">
+        <x:v>Generate a one-cycle pulse whenever each input bit makes a 0-to-1 transition.</x:v>
+      </x:c>
+      <x:c r="U98" s="168"/>
+    </x:row>
+    <x:row r="99" ht="42" customHeight="1">
       <x:c r="A99" s="135" t="n">
         <x:v>94</x:v>
       </x:c>
@@ -7014,21 +7760,28 @@
       <x:c r="O99" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P99" s="140" t="str">
-        <x:v>../../problems/Day 04/094-edgedetect2.md</x:v>
-      </x:c>
-      <x:c r="Q99" s="140" t="str">
-        <x:v>../../images/Day 04/094-edgedetect2.png</x:v>
-      </x:c>
-      <x:c r="R99" s="140" t="str">
-        <x:v>../../solutions/Day 04/094-edgedetect2.sv</x:v>
-      </x:c>
-      <x:c r="S99" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/edgedetect2</x:v>
-      </x:c>
-      <x:c r="T99" s="141" t="str"/>
-    </x:row>
-    <x:row r="100" ht="34" customHeight="1">
+      <x:c r="P99" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/094-edgedetect2.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/094-edgedetect2.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q99" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/094-edgedetect2.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/094-edgedetect2.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R99" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/094-edgedetect2.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/094-edgedetect2.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S99" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/edgedetect2","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/edgedetect2, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T99" s="162" t="str">
+        <x:v>Generate a one-cycle pulse whenever each input bit changes in either direction.</x:v>
+      </x:c>
+      <x:c r="U99" s="168"/>
+    </x:row>
+    <x:row r="100" ht="42" customHeight="1">
       <x:c r="A100" s="135" t="n">
         <x:v>95</x:v>
       </x:c>
@@ -7074,21 +7827,28 @@
       <x:c r="O100" s="139" t="n">
         <x:v>0.14</x:v>
       </x:c>
-      <x:c r="P100" s="140" t="str">
-        <x:v>../../problems/Day 04/095-edgecapture.md</x:v>
-      </x:c>
-      <x:c r="Q100" s="140" t="str">
-        <x:v>../../images/Day 04/095-edgecapture.png</x:v>
-      </x:c>
-      <x:c r="R100" s="140" t="str">
-        <x:v>../../solutions/Day 04/095-edgecapture.sv</x:v>
-      </x:c>
-      <x:c r="S100" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/edgecapture</x:v>
-      </x:c>
-      <x:c r="T100" s="141" t="str"/>
-    </x:row>
-    <x:row r="101" ht="34" customHeight="1">
+      <x:c r="P100" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/095-edgecapture.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/095-edgecapture.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q100" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/095-edgecapture.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/095-edgecapture.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R100" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/095-edgecapture.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/095-edgecapture.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S100" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/edgecapture","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/edgecapture, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T100" s="162" t="str">
+        <x:v>Set a register bit when a falling edge occurs and keep it set until a synchronous reset clears it.</x:v>
+      </x:c>
+      <x:c r="U100" s="168"/>
+    </x:row>
+    <x:row r="101" ht="42" customHeight="1">
       <x:c r="A101" s="135" t="n">
         <x:v>96</x:v>
       </x:c>
@@ -7134,21 +7894,28 @@
       <x:c r="O101" s="139" t="n">
         <x:v>0.14</x:v>
       </x:c>
-      <x:c r="P101" s="140" t="str">
-        <x:v>../../problems/Day 04/096-dualedge.md</x:v>
-      </x:c>
-      <x:c r="Q101" s="140" t="str">
-        <x:v>../../images/Day 04/096-dualedge.png</x:v>
-      </x:c>
-      <x:c r="R101" s="140" t="str">
-        <x:v>../../solutions/Day 04/096-dualedge.sv</x:v>
-      </x:c>
-      <x:c r="S101" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/dualedge</x:v>
-      </x:c>
-      <x:c r="T101" s="141" t="str"/>
-    </x:row>
-    <x:row r="102" ht="34" customHeight="1">
+      <x:c r="P101" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/096-dualedge.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/096-dualedge.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q101" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/096-dualedge.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/096-dualedge.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R101" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/096-dualedge.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/096-dualedge.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S101" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/dualedge","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dualedge, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T101" s="162" t="str">
+        <x:v>Emulate dual-edge-triggered storage using logic that captures data on both rising and falling clock edges.</x:v>
+      </x:c>
+      <x:c r="U101" s="168"/>
+    </x:row>
+    <x:row r="102" ht="42" customHeight="1">
       <x:c r="A102" s="135" t="n">
         <x:v>97</x:v>
       </x:c>
@@ -7194,21 +7961,28 @@
       <x:c r="O102" s="139" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P102" s="140" t="str">
-        <x:v>../../problems/Day 04/097-count15.md</x:v>
-      </x:c>
-      <x:c r="Q102" s="140" t="str">
-        <x:v>../../images/Day 04/097-count15.png</x:v>
-      </x:c>
-      <x:c r="R102" s="140" t="str">
-        <x:v>../../solutions/Day 04/097-count15.sv</x:v>
-      </x:c>
-      <x:c r="S102" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/count15</x:v>
-      </x:c>
-      <x:c r="T102" s="141" t="str"/>
-    </x:row>
-    <x:row r="103" ht="34" customHeight="1">
+      <x:c r="P102" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/097-count15.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/097-count15.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q102" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/097-count15.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/097-count15.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R102" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/097-count15.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/097-count15.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S102" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/count15","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/count15, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T102" s="162" t="str">
+        <x:v>Implement a 4-bit binary counter with synchronous reset that naturally wraps after 15.</x:v>
+      </x:c>
+      <x:c r="U102" s="168"/>
+    </x:row>
+    <x:row r="103" ht="42" customHeight="1">
       <x:c r="A103" s="135" t="n">
         <x:v>98</x:v>
       </x:c>
@@ -7254,21 +8028,28 @@
       <x:c r="O103" s="139" t="n">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P103" s="140" t="str">
-        <x:v>../../problems/Day 04/098-count10.md</x:v>
-      </x:c>
-      <x:c r="Q103" s="140" t="str">
-        <x:v>../../images/Day 04/098-count10.png</x:v>
-      </x:c>
-      <x:c r="R103" s="140" t="str">
-        <x:v>../../solutions/Day 04/098-count10.sv</x:v>
-      </x:c>
-      <x:c r="S103" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/count10</x:v>
-      </x:c>
-      <x:c r="T103" s="141" t="str"/>
-    </x:row>
-    <x:row r="104" ht="34" customHeight="1">
+      <x:c r="P103" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/098-count10.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/098-count10.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q103" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/098-count10.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/098-count10.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R103" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/098-count10.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/098-count10.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S103" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/count10","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/count10, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T103" s="162" t="str">
+        <x:v>Implement a decade counter that counts from 0 through 9 and then wraps to 0.</x:v>
+      </x:c>
+      <x:c r="U103" s="168"/>
+    </x:row>
+    <x:row r="104" ht="42" customHeight="1">
       <x:c r="A104" s="135" t="n">
         <x:v>99</x:v>
       </x:c>
@@ -7314,21 +8095,28 @@
       <x:c r="O104" s="139" t="n">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P104" s="140" t="str">
-        <x:v>../../problems/Day 04/099-count1to10.md</x:v>
-      </x:c>
-      <x:c r="Q104" s="140" t="str">
-        <x:v>../../images/Day 04/099-count1to10.png</x:v>
-      </x:c>
-      <x:c r="R104" s="140" t="str">
-        <x:v>../../solutions/Day 04/099-count1to10.sv</x:v>
-      </x:c>
-      <x:c r="S104" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/count1to10</x:v>
-      </x:c>
-      <x:c r="T104" s="141" t="str"/>
-    </x:row>
-    <x:row r="105" ht="34" customHeight="1">
+      <x:c r="P104" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/099-count1to10.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/099-count1to10.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q104" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/099-count1to10.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/099-count1to10.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R104" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/099-count1to10.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/099-count1to10.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S104" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/count1to10","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/count1to10, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T104" s="162" t="str">
+        <x:v>Implement the specified 1-to-10 decade count sequence with the required reset and enable behaviour.</x:v>
+      </x:c>
+      <x:c r="U104" s="168"/>
+    </x:row>
+    <x:row r="105" ht="42" customHeight="1">
       <x:c r="A105" s="135" t="n">
         <x:v>100</x:v>
       </x:c>
@@ -7374,21 +8162,28 @@
       <x:c r="O105" s="139" t="n">
         <x:v>0.67</x:v>
       </x:c>
-      <x:c r="P105" s="140" t="str">
-        <x:v>../../problems/Day 04/100-countslow.md</x:v>
-      </x:c>
-      <x:c r="Q105" s="140" t="str">
-        <x:v>../../images/Day 04/100-countslow.png</x:v>
-      </x:c>
-      <x:c r="R105" s="140" t="str">
-        <x:v>../../solutions/Day 04/100-countslow.sv</x:v>
-      </x:c>
-      <x:c r="S105" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/countslow</x:v>
-      </x:c>
-      <x:c r="T105" s="141" t="str"/>
-    </x:row>
-    <x:row r="106" ht="34" customHeight="1">
+      <x:c r="P105" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/100-countslow.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/100-countslow.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q105" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/100-countslow.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/100-countslow.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R105" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/100-countslow.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/100-countslow.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S105" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/countslow","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/countslow, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T105" s="162" t="str">
+        <x:v>Create a decade counter that advances only when the slow-enable input is asserted.</x:v>
+      </x:c>
+      <x:c r="U105" s="168"/>
+    </x:row>
+    <x:row r="106" ht="42" customHeight="1">
       <x:c r="A106" s="135" t="n">
         <x:v>101</x:v>
       </x:c>
@@ -7434,21 +8229,28 @@
       <x:c r="O106" s="139" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P106" s="140" t="str">
-        <x:v>../../problems/Day 04/101-shift4.md</x:v>
-      </x:c>
-      <x:c r="Q106" s="140" t="str">
-        <x:v>../../images/Day 04/101-shift4.png</x:v>
-      </x:c>
-      <x:c r="R106" s="140" t="str">
-        <x:v>../../solutions/Day 04/101-shift4.sv</x:v>
-      </x:c>
-      <x:c r="S106" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/shift4</x:v>
-      </x:c>
-      <x:c r="T106" s="141" t="str"/>
-    </x:row>
-    <x:row r="107" ht="34" customHeight="1">
+      <x:c r="P106" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/101-shift4.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/101-shift4.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q106" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/101-shift4.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/101-shift4.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R106" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/101-shift4.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/101-shift4.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S106" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/shift4","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/shift4, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T106" s="162" t="str">
+        <x:v>Build a 4-bit shift register with the specified load/shift controls and expose the requested stage output.</x:v>
+      </x:c>
+      <x:c r="U106" s="168"/>
+    </x:row>
+    <x:row r="107" ht="42" customHeight="1">
       <x:c r="A107" s="135" t="n">
         <x:v>102</x:v>
       </x:c>
@@ -7494,21 +8296,28 @@
       <x:c r="O107" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P107" s="140" t="str">
-        <x:v>../../problems/Day 04/102-rotate100.md</x:v>
-      </x:c>
-      <x:c r="Q107" s="140" t="str">
-        <x:v>../../images/Day 04/102-rotate100.png</x:v>
-      </x:c>
-      <x:c r="R107" s="140" t="str">
-        <x:v>../../solutions/Day 04/102-rotate100.sv</x:v>
-      </x:c>
-      <x:c r="S107" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/rotate100</x:v>
-      </x:c>
-      <x:c r="T107" s="141" t="str"/>
-    </x:row>
-    <x:row r="108" ht="34" customHeight="1">
+      <x:c r="P107" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/102-rotate100.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/102-rotate100.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q107" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/102-rotate100.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/102-rotate100.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R107" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/102-rotate100.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/102-rotate100.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S107" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/rotate100","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/rotate100, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T107" s="162" t="str">
+        <x:v>Build a 100-bit register that can hold, load, rotate left, or rotate right according to the controls.</x:v>
+      </x:c>
+      <x:c r="U107" s="168"/>
+    </x:row>
+    <x:row r="108" ht="42" customHeight="1">
       <x:c r="A108" s="135" t="n">
         <x:v>103</x:v>
       </x:c>
@@ -7554,21 +8363,28 @@
       <x:c r="O108" s="139" t="n">
         <x:v>0.17</x:v>
       </x:c>
-      <x:c r="P108" s="140" t="str">
-        <x:v>../../problems/Day 04/103-shift18.md</x:v>
-      </x:c>
-      <x:c r="Q108" s="140" t="str">
-        <x:v>../../images/Day 04/103-shift18.png</x:v>
-      </x:c>
-      <x:c r="R108" s="140" t="str">
-        <x:v>../../solutions/Day 04/103-shift18.sv</x:v>
-      </x:c>
-      <x:c r="S108" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/shift18</x:v>
-      </x:c>
-      <x:c r="T108" s="141" t="str"/>
-    </x:row>
-    <x:row r="109" ht="34" customHeight="1">
+      <x:c r="P108" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/103-shift18.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/103-shift18.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q108" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/103-shift18.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/103-shift18.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R108" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/103-shift18.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/103-shift18.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S108" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/shift18","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/shift18, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T108" s="162" t="str">
+        <x:v>Build a 64-bit register that can load or perform left/right arithmetic shifts by either 1 or 8 positions.</x:v>
+      </x:c>
+      <x:c r="U108" s="168"/>
+    </x:row>
+    <x:row r="109" ht="42" customHeight="1">
       <x:c r="A109" s="135" t="n">
         <x:v>104</x:v>
       </x:c>
@@ -7614,21 +8430,28 @@
       <x:c r="O109" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P109" s="140" t="str">
-        <x:v>../../problems/Day 04/104-lfsr5.md</x:v>
-      </x:c>
-      <x:c r="Q109" s="140" t="str">
-        <x:v>../../images/Day 04/104-lfsr5.png</x:v>
-      </x:c>
-      <x:c r="R109" s="140" t="str">
-        <x:v>../../solutions/Day 04/104-lfsr5.sv</x:v>
-      </x:c>
-      <x:c r="S109" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/lfsr5</x:v>
-      </x:c>
-      <x:c r="T109" s="141" t="str"/>
-    </x:row>
-    <x:row r="110" ht="34" customHeight="1">
+      <x:c r="P109" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/104-lfsr5.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/104-lfsr5.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q109" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/104-lfsr5.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/104-lfsr5.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R109" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/104-lfsr5.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/104-lfsr5.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S109" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/lfsr5","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/lfsr5, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T109" s="162" t="str">
+        <x:v>Implement the specified 5-bit linear-feedback shift register using the given feedback taps and reset state.</x:v>
+      </x:c>
+      <x:c r="U109" s="168"/>
+    </x:row>
+    <x:row r="110" ht="42" customHeight="1">
       <x:c r="A110" s="135" t="n">
         <x:v>105</x:v>
       </x:c>
@@ -7674,21 +8497,28 @@
       <x:c r="O110" s="139" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P110" s="140" t="str">
-        <x:v>../../problems/Day 04/105-mt2015_lfsr.md</x:v>
-      </x:c>
-      <x:c r="Q110" s="140" t="str">
-        <x:v>../../images/Day 04/105-mt2015_lfsr.png</x:v>
-      </x:c>
-      <x:c r="R110" s="140" t="str">
-        <x:v>../../solutions/Day 04/105-mt2015_lfsr.sv</x:v>
-      </x:c>
-      <x:c r="S110" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/mt2015_lfsr</x:v>
-      </x:c>
-      <x:c r="T110" s="141" t="str"/>
-    </x:row>
-    <x:row r="111" ht="34" customHeight="1">
+      <x:c r="P110" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/105-mt2015_lfsr.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/105-mt2015_lfsr.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q110" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/105-mt2015_lfsr.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/105-mt2015_lfsr.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R110" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/105-mt2015_lfsr.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/105-mt2015_lfsr.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S110" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mt2015_lfsr","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_lfsr, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T110" s="162" t="str">
+        <x:v>Implement the shown 3-bit LFSR and reproduce its required feedback sequence.</x:v>
+      </x:c>
+      <x:c r="U110" s="168"/>
+    </x:row>
+    <x:row r="111" ht="42" customHeight="1">
       <x:c r="A111" s="135" t="n">
         <x:v>106</x:v>
       </x:c>
@@ -7734,21 +8564,28 @@
       <x:c r="O111" s="139" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P111" s="140" t="str">
-        <x:v>../../problems/Day 04/106-lfsr32.md</x:v>
-      </x:c>
-      <x:c r="Q111" s="140" t="str">
-        <x:v>../../images/Day 04/106-lfsr32.png</x:v>
-      </x:c>
-      <x:c r="R111" s="140" t="str">
-        <x:v>../../solutions/Day 04/106-lfsr32.sv</x:v>
-      </x:c>
-      <x:c r="S111" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/lfsr32</x:v>
-      </x:c>
-      <x:c r="T111" s="141" t="str"/>
-    </x:row>
-    <x:row r="112" ht="34" customHeight="1">
+      <x:c r="P111" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/106-lfsr32.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/106-lfsr32.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q111" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/106-lfsr32.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/106-lfsr32.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R111" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/106-lfsr32.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/106-lfsr32.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S111" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/lfsr32","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/lfsr32, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T111" s="162" t="str">
+        <x:v>Implement a 32-bit linear-feedback shift register with the specified tap positions.</x:v>
+      </x:c>
+      <x:c r="U111" s="168"/>
+    </x:row>
+    <x:row r="112" ht="42" customHeight="1">
       <x:c r="A112" s="135" t="n">
         <x:v>107</x:v>
       </x:c>
@@ -7794,21 +8631,28 @@
       <x:c r="O112" s="139" t="n">
         <x:v>0.13</x:v>
       </x:c>
-      <x:c r="P112" s="140" t="str">
-        <x:v>../../problems/Day 04/107-exams__m2014_q4k.md</x:v>
-      </x:c>
-      <x:c r="Q112" s="140" t="str">
-        <x:v>../../images/Day 04/107-exams__m2014_q4k.png</x:v>
-      </x:c>
-      <x:c r="R112" s="140" t="str">
-        <x:v>../../solutions/Day 04/107-exams__m2014_q4k.sv</x:v>
-      </x:c>
-      <x:c r="S112" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/m2014_q4k</x:v>
-      </x:c>
-      <x:c r="T112" s="141" t="str"/>
-    </x:row>
-    <x:row r="113" ht="34" customHeight="1">
+      <x:c r="P112" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/107-exams__m2014_q4k.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2004/107-exams__m2014_q4k.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q112" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/107-exams__m2014_q4k.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2004/107-exams__m2014_q4k.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R112" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/107-exams__m2014_q4k.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2004/107-exams__m2014_q4k.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S112" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4k","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4k, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T112" s="162" t="str">
+        <x:v>Translate the exam shift-register schematic into clocked Verilog with the same data movement.</x:v>
+      </x:c>
+      <x:c r="U112" s="168"/>
+    </x:row>
+    <x:row r="113" ht="42" customHeight="1">
       <x:c r="A113" s="135" t="n">
         <x:v>108</x:v>
       </x:c>
@@ -7854,21 +8698,28 @@
       <x:c r="O113" s="139" t="n">
         <x:v>0.17</x:v>
       </x:c>
-      <x:c r="P113" s="140" t="str">
-        <x:v>../../problems/Day 05/108-exams__2014_q4b.md</x:v>
-      </x:c>
-      <x:c r="Q113" s="140" t="str">
-        <x:v>../../images/Day 05/108-exams__2014_q4b.png</x:v>
-      </x:c>
-      <x:c r="R113" s="140" t="str">
-        <x:v>../../solutions/Day 05/108-exams__2014_q4b.sv</x:v>
-      </x:c>
-      <x:c r="S113" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/2014_q4b</x:v>
-      </x:c>
-      <x:c r="T113" s="141" t="str"/>
-    </x:row>
-    <x:row r="114" ht="34" customHeight="1">
+      <x:c r="P113" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2005/108-exams__2014_q4b.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2005/108-exams__2014_q4b.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q113" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2005/108-exams__2014_q4b.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2005/108-exams__2014_q4b.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R113" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2005/108-exams__2014_q4b.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2005/108-exams__2014_q4b.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S113" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2014_q4b","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2014_q4b, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T113" s="162" t="str">
+        <x:v>Implement the shown shift register and its control logic exactly as specified by the exam circuit.</x:v>
+      </x:c>
+      <x:c r="U113" s="168"/>
+    </x:row>
+    <x:row r="114" ht="42" customHeight="1">
       <x:c r="A114" s="135" t="n">
         <x:v>109</x:v>
       </x:c>
@@ -7914,21 +8765,28 @@
       <x:c r="O114" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P114" s="140" t="str">
-        <x:v>../../problems/Day 05/109-exams__ece241_2013_q12.md</x:v>
-      </x:c>
-      <x:c r="Q114" s="140" t="str">
-        <x:v>../../images/Day 05/109-exams__ece241_2013_q12.png</x:v>
-      </x:c>
-      <x:c r="R114" s="140" t="str">
-        <x:v>../../solutions/Day 05/109-exams__ece241_2013_q12.sv</x:v>
-      </x:c>
-      <x:c r="S114" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/exams/ece241_2013_q12</x:v>
-      </x:c>
-      <x:c r="T114" s="141" t="str"/>
-    </x:row>
-    <x:row r="115" ht="34" customHeight="1">
+      <x:c r="P114" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2005/109-exams__ece241_2013_q12.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2005/109-exams__ece241_2013_q12.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q114" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2005/109-exams__ece241_2013_q12.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2005/109-exams__ece241_2013_q12.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R114" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2005/109-exams__ece241_2013_q12.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2005/109-exams__ece241_2013_q12.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S114" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2013_q12","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2013_q12, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T114" s="162" t="str">
+        <x:v>Build a 3-input lookup table from a shift register and multiplexer so its truth table can be loaded serially.</x:v>
+      </x:c>
+      <x:c r="U114" s="168"/>
+    </x:row>
+    <x:row r="115" ht="42" customHeight="1">
       <x:c r="A115" s="135" t="n">
         <x:v>110</x:v>
       </x:c>
@@ -7974,21 +8832,28 @@
       <x:c r="O115" s="139" t="n">
         <x:v>0.11</x:v>
       </x:c>
-      <x:c r="P115" s="140" t="str">
-        <x:v>../../problems/Day 05/110-fsm1.md</x:v>
-      </x:c>
-      <x:c r="Q115" s="140" t="str">
-        <x:v>../../images/Day 05/110-fsm1.png</x:v>
-      </x:c>
-      <x:c r="R115" s="140" t="str">
-        <x:v>../../solutions/Day 05/110-fsm1.sv</x:v>
-      </x:c>
-      <x:c r="S115" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/fsm1</x:v>
-      </x:c>
-      <x:c r="T115" s="141" t="str"/>
-    </x:row>
-    <x:row r="116" ht="34" customHeight="1">
+      <x:c r="P115" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2005/110-fsm1.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2005/110-fsm1.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q115" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2005/110-fsm1.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2005/110-fsm1.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R115" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2005/110-fsm1.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2005/110-fsm1.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S115" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm1","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm1, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T115" s="162" t="str">
+        <x:v>Implement the provided two-state FSM, using an asynchronous reset and the diagram's transition and output rules.</x:v>
+      </x:c>
+      <x:c r="U115" s="168"/>
+    </x:row>
+    <x:row r="116" ht="42" customHeight="1">
       <x:c r="A116" s="135" t="n">
         <x:v>111</x:v>
       </x:c>
@@ -8034,21 +8899,28 @@
       <x:c r="O116" s="139" t="n">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P116" s="140" t="str">
-        <x:v>../../problems/Day 05/111-fsm1s.md</x:v>
-      </x:c>
-      <x:c r="Q116" s="140" t="str">
-        <x:v>../../images/Day 05/111-fsm1s.png</x:v>
-      </x:c>
-      <x:c r="R116" s="140" t="str">
-        <x:v>../../solutions/Day 05/111-fsm1s.sv</x:v>
-      </x:c>
-      <x:c r="S116" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/fsm1s</x:v>
-      </x:c>
-      <x:c r="T116" s="141" t="str"/>
-    </x:row>
-    <x:row r="117" ht="34" customHeight="1">
+      <x:c r="P116" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2005/111-fsm1s.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2005/111-fsm1s.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q116" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2005/111-fsm1s.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2005/111-fsm1s.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R116" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2005/111-fsm1s.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2005/111-fsm1s.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S116" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm1s","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm1s, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T116" s="162" t="str">
+        <x:v>Implement the same two-state FSM with a synchronous reset instead of an asynchronous reset.</x:v>
+      </x:c>
+      <x:c r="U116" s="168"/>
+    </x:row>
+    <x:row r="117" ht="42" customHeight="1">
       <x:c r="A117" s="135" t="n">
         <x:v>112</x:v>
       </x:c>
@@ -8094,21 +8966,28 @@
       <x:c r="O117" s="139" t="n">
         <x:v>0.17</x:v>
       </x:c>
-      <x:c r="P117" s="140" t="str">
-        <x:v>../../problems/Day 05/112-fsm2.md</x:v>
-      </x:c>
-      <x:c r="Q117" s="140" t="str">
-        <x:v>../../images/Day 05/112-fsm2.png</x:v>
-      </x:c>
-      <x:c r="R117" s="140" t="str">
-        <x:v>../../solutions/Day 05/112-fsm2.sv</x:v>
-      </x:c>
-      <x:c r="S117" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/fsm2</x:v>
-      </x:c>
-      <x:c r="T117" s="141" t="str"/>
-    </x:row>
-    <x:row r="118" ht="34" customHeight="1">
+      <x:c r="P117" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2005/112-fsm2.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2005/112-fsm2.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q117" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2005/112-fsm2.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2005/112-fsm2.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R117" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2005/112-fsm2.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2005/112-fsm2.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S117" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm2","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm2, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T117" s="162" t="str">
+        <x:v>Implement the second supplied finite-state machine, including its asynchronous reset, transitions, and output decoding.</x:v>
+      </x:c>
+      <x:c r="U117" s="168"/>
+    </x:row>
+    <x:row r="118" ht="42" customHeight="1">
       <x:c r="A118" s="135" t="n">
         <x:v>113</x:v>
       </x:c>
@@ -8154,21 +9033,28 @@
       <x:c r="O118" s="139" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P118" s="140" t="str">
-        <x:v>../../problems/Day 05/113-fsm2s.md</x:v>
-      </x:c>
-      <x:c r="Q118" s="140" t="str">
-        <x:v>../../images/Day 05/113-fsm2s.png</x:v>
-      </x:c>
-      <x:c r="R118" s="140" t="str">
-        <x:v>../../solutions/Day 05/113-fsm2s.sv</x:v>
-      </x:c>
-      <x:c r="S118" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/fsm2s</x:v>
-      </x:c>
-      <x:c r="T118" s="141" t="str"/>
-    </x:row>
-    <x:row r="119" ht="34" customHeight="1">
+      <x:c r="P118" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2005/113-fsm2s.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2005/113-fsm2s.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q118" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2005/113-fsm2s.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2005/113-fsm2s.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R118" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2005/113-fsm2s.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2005/113-fsm2s.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S118" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm2s","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm2s, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T118" s="162" t="str">
+        <x:v>Implement the second FSM with a synchronous reset while preserving the transition and output behaviour.</x:v>
+      </x:c>
+      <x:c r="U118" s="168"/>
+    </x:row>
+    <x:row r="119" ht="42" customHeight="1">
       <x:c r="A119" s="135" t="n">
         <x:v>114</x:v>
       </x:c>
@@ -8214,21 +9100,28 @@
       <x:c r="O119" s="139" t="n">
         <x:v>0.14</x:v>
       </x:c>
-      <x:c r="P119" s="140" t="str">
-        <x:v>../../problems/Day 05/114-fsm3comb.md</x:v>
-      </x:c>
-      <x:c r="Q119" s="140" t="str">
-        <x:v>../../images/Day 05/114-fsm3comb.png</x:v>
-      </x:c>
-      <x:c r="R119" s="140" t="str">
-        <x:v>../../solutions/Day 05/114-fsm3comb.sv</x:v>
-      </x:c>
-      <x:c r="S119" s="140" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/fsm3comb</x:v>
-      </x:c>
-      <x:c r="T119" s="141" t="str"/>
-    </x:row>
-    <x:row r="120" ht="34" customHeight="1">
+      <x:c r="P119" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2005/114-fsm3comb.md","Open note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2005/114-fsm3comb.md, friendlyName=Open note</x:v>
+      </x:c>
+      <x:c r="Q119" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2005/114-fsm3comb.png","Full-size image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2005/114-fsm3comb.png, friendlyName=Full-size image</x:v>
+      </x:c>
+      <x:c r="R119" s="153" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2005/114-fsm3comb.sv","Open solution")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2005/114-fsm3comb.sv, friendlyName=Open solution</x:v>
+      </x:c>
+      <x:c r="S119" s="153" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm3comb","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm3comb, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T119" s="162" t="str">
+        <x:v>Write only the combinational next-state logic for the supplied state-transition diagram.</x:v>
+      </x:c>
+      <x:c r="U119" s="168"/>
+    </x:row>
+    <x:row r="120" ht="42" customHeight="1">
       <x:c r="A120" s="142" t="n">
         <x:v>115</x:v>
       </x:c>
@@ -8268,18 +9161,22 @@
       <x:c r="O120" s="146" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P120" s="147" t="str"/>
-      <x:c r="Q120" s="147" t="str"/>
-      <x:c r="R120" s="147" t="str"/>
-      <x:c r="S120" s="147" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/fsm3onehot</x:v>
-      </x:c>
-      <x:c r="T120" s="148" t="str"/>
+      <x:c r="P120" s="154"/>
+      <x:c r="Q120" s="154"/>
+      <x:c r="R120" s="154"/>
+      <x:c r="S120" s="154" t="e">
+        <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm3onehot","HDLBits")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm3onehot, friendlyName=HDLBits</x:v>
+      </x:c>
+      <x:c r="T120" s="163" t="str">
+        <x:v>Implement the supplied FSM's combinational next-state equations using one-hot state encoding.</x:v>
+      </x:c>
+      <x:c r="U120" s="168"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:T2"/>
-    <x:mergeCell ref="A3:T3"/>
+    <x:mergeCell ref="A1:U1"/>
+    <x:mergeCell ref="A3:U3"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="G6:G120">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Completed"/>
@@ -8299,7 +9196,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R366b1bb48450413c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf058414ac6b5407b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/hdlbits-archive/HDLBits_Tracker.xlsx
+++ b/outputs/hdlbits-archive/HDLBits_Tracker.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rda21839dd2fb4ae6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="2" r:id="R641a44991dc64ffa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R06f55543237b4f7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="2" r:id="R620c29682a984bc1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
     <x:numFmt numFmtId="201" formatCode="0%"/>
     <x:numFmt numFmtId="202" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -100,8 +100,13 @@
       <x:color rgb="FF0563C1"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F1F1F"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -136,6 +141,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFF99"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFCCFFCC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E1F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -190,7 +210,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="119">
+  <x:cellXfs count="130">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -504,6 +524,17 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="14" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="14" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -514,7 +545,7 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFCCFFCC"/>
         </x:patternFill>
       </x:fill>
@@ -525,7 +556,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFFF99"/>
         </x:patternFill>
       </x:fill>
@@ -535,7 +566,7 @@
         <x:color rgb="FF666666"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF3F3F3"/>
         </x:patternFill>
       </x:fill>
@@ -545,7 +576,7 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFCCFFCC"/>
         </x:patternFill>
       </x:fill>
@@ -814,7 +845,7 @@
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="92" t="str">
         <x:f>"Exact website sequence · "&amp;A6&amp;" of "&amp;D6&amp;" completed · "&amp;B6&amp;" review · "&amp;C6&amp;" to do"</x:f>
-        <x:v>Exact website sequence · 140 of 178 completed · 1 review · 37 to do</x:v>
+        <x:v>Exact website sequence · 141 of 178 completed · 2 review · 35 to do</x:v>
       </x:c>
       <x:c r="B3" s="92"/>
       <x:c r="C3" s="92"/>
@@ -850,15 +881,15 @@
     <x:row r="6" ht="28" customHeight="1">
       <x:c r="A6" s="97" t="n">
         <x:f>COUNTIF('Tracker'!$G$6:$G$260,"Completed")</x:f>
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B6" s="97" t="n">
         <x:f>COUNTIF('Tracker'!$G$6:$G$260,"Review")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="97" t="n">
         <x:f>COUNTIF('Tracker'!$G$6:$G$260,"To Do")</x:f>
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D6" s="97" t="n">
         <x:f>COUNTA('Tracker'!$F$6:$F$260)</x:f>
@@ -868,7 +899,7 @@
         <x:v>Problem</x:v>
       </x:c>
       <x:c r="G6" s="106" t="str">
-        <x:v>Lemmings 2</x:v>
+        <x:v>Lemmings 2; Q2a: FSM</x:v>
       </x:c>
       <x:c r="H6" s="106"/>
     </x:row>
@@ -877,7 +908,7 @@
         <x:v>Status</x:v>
       </x:c>
       <x:c r="G7" s="106" t="str">
-        <x:v>Review — 7 unsuccessful attempts</x:v>
+        <x:v>Review - 10 unsuccessful attempts</x:v>
       </x:c>
       <x:c r="H7" s="106"/>
     </x:row>
@@ -892,7 +923,7 @@
         <x:v>Source</x:v>
       </x:c>
       <x:c r="G8" s="107" t="str">
-        <x:v>https://hdlbits.01xz.net/wiki/lemmings2</x:v>
+        <x:v>Review.md</x:v>
       </x:c>
       <x:c r="H8" s="107"/>
     </x:row>
@@ -1076,6 +1107,16 @@
       </x:c>
     </x:row>
     <x:row r="17">
+      <x:c r="A17" s="125" t="str">
+        <x:v>Day 07</x:v>
+      </x:c>
+      <x:c r="B17" s="128" t="n">
+        <x:v>46202</x:v>
+      </x:c>
+      <x:c r="C17" s="129" t="n">
+        <x:f>COUNTIFS('Tracker'!$H$6:$H$260,A17,'Tracker'!$G$6:$G$260,"Completed")</x:f>
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E17" s="117" t="str">
         <x:v>Circuits</x:v>
       </x:c>
@@ -1212,7 +1253,7 @@
       </x:c>
       <x:c r="G25" s="118" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$260,E25,'Tracker'!$D$6:$D$260,F25,'Tracker'!$G$6:$G$260,"Completed")</x:f>
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H25" s="118" t="n">
         <x:f>COUNTIFS('Tracker'!$C$6:$C$260,E25,'Tracker'!$D$6:$D$260,F25)</x:f>
@@ -1462,7 +1503,7 @@
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="8" t="str">
         <x:f>"Website sequence verified: 178 of 178 IDs in exact order · "&amp;COUNTIF($G$6:$G$260,"Completed")&amp;" completed · "&amp;COUNTIF($G$6:$G$260,"Review")&amp;" review · "&amp;COUNTIF($G$6:$G$260,"To Do")&amp;" to do"</x:f>
-        <x:v>Website sequence verified: 178 of 178 IDs in exact order · 140 completed · 1 review · 37 to do</x:v>
+        <x:v>Website sequence verified: 178 of 178 IDs in exact order · 141 completed · 2 review · 35 to do</x:v>
       </x:c>
       <x:c r="B3" s="8"/>
       <x:c r="C3" s="8"/>
@@ -10878,7 +10919,9 @@
       <x:c r="A161" s="26" t="n">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="B161" s="26"/>
+      <x:c r="B161" s="26" t="n">
+        <x:v>142</x:v>
+      </x:c>
       <x:c r="C161" s="23" t="str">
         <x:v>Circuits</x:v>
       </x:c>
@@ -10892,33 +10935,50 @@
         <x:v>exams/ece241_2013_q8</x:v>
       </x:c>
       <x:c r="G161" s="26" t="str">
-        <x:v>To Do</x:v>
-      </x:c>
-      <x:c r="H161" s="26"/>
-      <x:c r="I161" s="32"/>
-      <x:c r="J161" s="26"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="H161" s="26" t="str">
+        <x:v>Day 07</x:v>
+      </x:c>
+      <x:c r="I161" s="32" t="n">
+        <x:v>46202</x:v>
+      </x:c>
+      <x:c r="J161" s="26" t="str">
+        <x:v>12:02:40 AM</x:v>
+      </x:c>
       <x:c r="K161" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L161" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="M161" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N161" s="26" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O161" s="35"/>
-      <x:c r="P161" s="29"/>
-      <x:c r="Q161" s="29"/>
-      <x:c r="R161" s="29"/>
+      <x:c r="O161" s="35" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="P161" s="29" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2007/142-exams__ece241_2013_q8.md","Note")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/problems/Day%2007/142-exams__ece241_2013_q8.md, friendlyName=Note</x:v>
+      </x:c>
+      <x:c r="Q161" s="29" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2007/142-exams__ece241_2013_q8.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Day%2007/142-exams__ece241_2013_q8.png, friendlyName=Image</x:v>
+      </x:c>
+      <x:c r="R161" s="29" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2007/142-exams__ece241_2013_q8.sv","Code")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/solutions/Day%2007/142-exams__ece241_2013_q8.sv, friendlyName=Code</x:v>
+      </x:c>
       <x:c r="S161" s="29" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2013_q8","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2013_q8, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T161" s="23" t="str">
-        <x:v>Not attempted yet. Read the HDLBits question, design the circuit or testbench, and obtain a successful submission.</x:v>
+        <x:v>Three-state Mealy detector for overlapping 101 with active-low asynchronous reset. State S10 plus input 1 asserts z in the detection cycle.</x:v>
       </x:c>
       <x:c r="U161" s="23"/>
     </x:row>
@@ -11420,33 +11480,41 @@
         <x:v>exams/2013_q2afsm</x:v>
       </x:c>
       <x:c r="G172" s="49" t="str">
-        <x:v>To Do</x:v>
+        <x:v>Review</x:v>
       </x:c>
       <x:c r="H172" s="49"/>
       <x:c r="I172" s="51"/>
       <x:c r="J172" s="49"/>
       <x:c r="K172" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L172" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M172" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N172" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O172" s="52"/>
-      <x:c r="P172" s="53"/>
-      <x:c r="Q172" s="53"/>
+      <x:c r="O172" s="52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P172" s="53" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/Review.md","Review")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/Review.md, friendlyName=Review</x:v>
+      </x:c>
+      <x:c r="Q172" s="53" t="e">
+        <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/images/Review/review-exams__2013_q2afsm.png","Image")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/images/Review/review-exams__2013_q2afsm.png, friendlyName=Image</x:v>
+      </x:c>
       <x:c r="R172" s="53"/>
       <x:c r="S172" s="53" t="e">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2013_q2afsm","HDLBits")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2013_q2afsm, friendlyName=HDLBits</x:v>
       </x:c>
       <x:c r="T172" s="50" t="str">
-        <x:v>Not attempted yet. Read the HDLBits question, design the circuit or testbench, and obtain a successful submission.</x:v>
+        <x:v>Attempted but not yet solved. Review the arbiter state diagram, request priority rules, and grant-hold behavior before resubmitting.</x:v>
       </x:c>
       <x:c r="U172" s="50"/>
     </x:row>
